--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C9CB12-162B-44C2-B387-745BB9CE6539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47267C0A-B9D1-4C12-8D07-7F7DE054A853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4142,7 +4142,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4585,7 +4585,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -21676,16 +21676,16 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D1223" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="A1:A602 A606:A1223">
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1223">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A602 A606:A1223">
-    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A664:A674">
     <cfRule type="duplicateValues" dxfId="4" priority="6"/>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47267C0A-B9D1-4C12-8D07-7F7DE054A853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B36C0D-CA60-4553-BC4E-B645810ECA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7035,7 +7035,7 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B178" t="s">
         <v>18</v>
@@ -10339,7 +10339,7 @@
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B414" t="s">
         <v>127</v>
@@ -15953,7 +15953,7 @@
     </row>
     <row r="815" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A815" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B815" s="3" t="s">
         <v>1345</v>
@@ -17717,7 +17717,7 @@
     </row>
     <row r="941" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A941" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B941" s="3" t="s">
         <v>1345</v>
@@ -18039,7 +18039,7 @@
     </row>
     <row r="964" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A964" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B964" s="3" t="s">
         <v>1345</v>
@@ -18123,7 +18123,7 @@
     </row>
     <row r="970" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A970" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B970" s="3" t="s">
         <v>1345</v>
@@ -20318,7 +20318,7 @@
     </row>
     <row r="1127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1127" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B1127" s="3" t="s">
         <v>1345</v>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DBDBB3-FB82-4B01-990E-0AECDA1DD47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEF8E2E-B99A-4338-9244-33AC1B9C28B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4823" uniqueCount="1334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4839" uniqueCount="1338">
   <si>
     <t>VINH</t>
   </si>
@@ -4023,13 +4023,25 @@
     <t>Phuong Tan Thanh</t>
   </si>
   <si>
-    <t>Phuong An Phu</t>
-  </si>
-  <si>
     <t>Phuong Thao Dien</t>
   </si>
   <si>
     <t>GO!</t>
+  </si>
+  <si>
+    <t>00399-FINELIFE URBAN HILL</t>
+  </si>
+  <si>
+    <t>04201-FINELIFE HA DO</t>
+  </si>
+  <si>
+    <t>04202-FINELIFE RIVIERA POINT</t>
+  </si>
+  <si>
+    <t>04205-FINELIFE LUMIERE AN PHU</t>
+  </si>
+  <si>
+    <t>FL</t>
   </si>
 </sst>
 </file>
@@ -4513,7 +4525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1206"/>
+  <dimension ref="A1:D1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -21268,7 +21280,7 @@
         <v>0</v>
       </c>
       <c r="B1197" s="4" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C1197" t="s">
         <v>505</v>
@@ -21282,7 +21294,7 @@
         <v>338</v>
       </c>
       <c r="B1198" s="4" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C1198" t="s">
         <v>552</v>
@@ -21296,7 +21308,7 @@
         <v>321</v>
       </c>
       <c r="B1199" s="4" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C1199" t="s">
         <v>472</v>
@@ -21310,7 +21322,7 @@
         <v>338</v>
       </c>
       <c r="B1200" s="4" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C1200" t="s">
         <v>573</v>
@@ -21324,7 +21336,7 @@
         <v>324</v>
       </c>
       <c r="B1201" s="4" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C1201" t="s">
         <v>382</v>
@@ -21338,7 +21350,7 @@
         <v>328</v>
       </c>
       <c r="B1202" s="4" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C1202" t="s">
         <v>329</v>
@@ -21352,7 +21364,7 @@
         <v>1</v>
       </c>
       <c r="B1203" s="4" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C1203" t="s">
         <v>1329</v>
@@ -21366,7 +21378,7 @@
         <v>338</v>
       </c>
       <c r="B1204" s="4" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C1204" t="s">
         <v>1330</v>
@@ -21380,10 +21392,10 @@
         <v>324</v>
       </c>
       <c r="B1205" s="4" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C1205" t="s">
-        <v>1331</v>
+        <v>325</v>
       </c>
       <c r="D1205" t="s">
         <v>1327</v>
@@ -21394,18 +21406,74 @@
         <v>324</v>
       </c>
       <c r="B1206" s="4" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C1206" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="D1206" t="s">
         <v>1328</v>
       </c>
     </row>
+    <row r="1207" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1207" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1207" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>381</v>
+      </c>
+      <c r="D1207" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1208" t="s">
+        <v>328</v>
+      </c>
+      <c r="B1208" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1208" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1209" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1209" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>382</v>
+      </c>
+      <c r="D1209" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1210" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1210" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1210" t="s">
+        <v>1336</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D1196" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="A1:A575 A579:A1206">
+  <conditionalFormatting sqref="A1:A575 A579:A1210">
     <cfRule type="duplicateValues" dxfId="11" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A637:A647">
@@ -21414,7 +21482,7 @@
   <conditionalFormatting sqref="A659:A661">
     <cfRule type="duplicateValues" dxfId="9" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1206">
+  <conditionalFormatting sqref="A1:A1210">
     <cfRule type="duplicateValues" dxfId="8" priority="406"/>
     <cfRule type="duplicateValues" dxfId="7" priority="407"/>
     <cfRule type="duplicateValues" dxfId="6" priority="408"/>
@@ -21422,7 +21490,7 @@
     <cfRule type="duplicateValues" dxfId="4" priority="410"/>
     <cfRule type="duplicateValues" dxfId="3" priority="411"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1206">
+  <conditionalFormatting sqref="B1:B1210">
     <cfRule type="duplicateValues" dxfId="2" priority="418"/>
     <cfRule type="duplicateValues" dxfId="1" priority="419"/>
     <cfRule type="duplicateValues" dxfId="0" priority="420"/>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEF8E2E-B99A-4338-9244-33AC1B9C28B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBDAF55-0A51-4B34-A342-32F73356F709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4525,7 +4525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1210"/>
+  <dimension ref="A1:E1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -4534,7 +4534,7 @@
     <col min="4" max="4" width="74.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>321</v>
       </c>
@@ -4547,8 +4547,11 @@
       <c r="D1" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1">
+        <v>10541</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>324</v>
       </c>
@@ -4561,8 +4564,11 @@
       <c r="D2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <v>11632</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>338</v>
       </c>
@@ -4575,8 +4581,11 @@
       <c r="D3" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3">
+        <v>11738</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>328</v>
       </c>
@@ -4590,7 +4599,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>324</v>
       </c>
@@ -4604,7 +4613,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -4618,7 +4627,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>335</v>
       </c>
@@ -4632,7 +4641,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>338</v>
       </c>
@@ -4646,7 +4655,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>338</v>
       </c>
@@ -4660,7 +4669,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>328</v>
       </c>
@@ -4674,7 +4683,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>338</v>
       </c>
@@ -4688,7 +4697,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -4702,7 +4711,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>324</v>
       </c>
@@ -4716,7 +4725,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -4730,7 +4739,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>335</v>
       </c>
@@ -4744,7 +4753,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>321</v>
       </c>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D156D406-D32D-4692-8F48-F044B6BB5B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503E35DD-DBCC-4DC9-9732-A5DFA9DC8091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1219</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4864" uniqueCount="1346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4876" uniqueCount="1349">
   <si>
     <t>VINH</t>
   </si>
@@ -4066,6 +4066,15 @@
   </si>
   <si>
     <t>BHX VO OANH</t>
+  </si>
+  <si>
+    <t>02219-CF NGUYEN VAN TANG 42</t>
+  </si>
+  <si>
+    <t>00309-CO-OPXTRA LONG BINH</t>
+  </si>
+  <si>
+    <t>00306-CO-OPXTRA PHAM VAN DONG</t>
   </si>
 </sst>
 </file>
@@ -4141,13 +4150,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4168,15 +4177,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4579,7 +4579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1216"/>
+  <dimension ref="A1:D1219"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -5390,7 +5390,7 @@
       <c r="A58" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="3" t="s">
         <v>1330</v>
       </c>
       <c r="C58" s="1" t="s">
@@ -5404,7 +5404,7 @@
       <c r="A59" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="3" t="s">
         <v>1335</v>
       </c>
       <c r="C59" s="1" t="s">
@@ -5740,7 +5740,7 @@
       <c r="A83" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="3" t="s">
         <v>1330</v>
       </c>
       <c r="C83" s="1" t="s">
@@ -8386,7 +8386,7 @@
       <c r="A272" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B272" s="11" t="s">
+      <c r="B272" s="3" t="s">
         <v>1330</v>
       </c>
       <c r="C272" s="1" t="s">
@@ -11214,7 +11214,7 @@
       <c r="A474" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B474" s="11" t="s">
+      <c r="B474" s="3" t="s">
         <v>1330</v>
       </c>
       <c r="C474" s="1" t="s">
@@ -11914,7 +11914,7 @@
       <c r="A524" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B524" s="12" t="s">
+      <c r="B524" s="5" t="s">
         <v>1330</v>
       </c>
       <c r="C524" s="1" t="s">
@@ -11928,7 +11928,7 @@
       <c r="A525" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B525" s="12" t="s">
+      <c r="B525" s="5" t="s">
         <v>1335</v>
       </c>
       <c r="C525" s="1" t="s">
@@ -13748,7 +13748,7 @@
       <c r="A655" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B655" s="12" t="s">
+      <c r="B655" s="5" t="s">
         <v>1330</v>
       </c>
       <c r="C655" s="1" t="s">
@@ -15820,7 +15820,7 @@
       <c r="A803" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B803" s="13" t="s">
+      <c r="B803" s="9" t="s">
         <v>1335</v>
       </c>
       <c r="C803" s="1" t="s">
@@ -16128,7 +16128,7 @@
       <c r="A825" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B825" s="13" t="s">
+      <c r="B825" s="9" t="s">
         <v>1330</v>
       </c>
       <c r="C825" s="1" t="s">
@@ -16142,7 +16142,7 @@
       <c r="A826" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B826" s="13" t="s">
+      <c r="B826" s="9" t="s">
         <v>1335</v>
       </c>
       <c r="C826" s="1" t="s">
@@ -17136,7 +17136,7 @@
       <c r="A897" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B897" s="13" t="s">
+      <c r="B897" s="9" t="s">
         <v>1330</v>
       </c>
       <c r="C897" s="1" t="s">
@@ -18550,7 +18550,7 @@
       <c r="A998" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B998" s="13" t="s">
+      <c r="B998" s="9" t="s">
         <v>1330</v>
       </c>
       <c r="C998" s="1" t="s">
@@ -18900,7 +18900,7 @@
       <c r="A1023" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B1023" s="13" t="s">
+      <c r="B1023" s="9" t="s">
         <v>1330</v>
       </c>
       <c r="C1023" s="1" t="s">
@@ -21518,7 +21518,7 @@
       <c r="A1210" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1210" s="13" t="s">
+      <c r="B1210" s="9" t="s">
         <v>1343</v>
       </c>
       <c r="C1210" t="s">
@@ -21532,7 +21532,7 @@
       <c r="A1211" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B1211" s="13" t="s">
+      <c r="B1211" s="9" t="s">
         <v>1343</v>
       </c>
       <c r="C1211" t="s">
@@ -21546,7 +21546,7 @@
       <c r="A1212" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1212" s="13" t="s">
+      <c r="B1212" s="9" t="s">
         <v>1343</v>
       </c>
       <c r="C1212" t="s">
@@ -21560,7 +21560,7 @@
       <c r="A1213" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1213" s="13" t="s">
+      <c r="B1213" s="9" t="s">
         <v>1343</v>
       </c>
       <c r="C1213" t="s">
@@ -21574,7 +21574,7 @@
       <c r="A1214" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1214" s="13" t="s">
+      <c r="B1214" s="9" t="s">
         <v>1343</v>
       </c>
       <c r="C1214" t="s">
@@ -21588,7 +21588,7 @@
       <c r="A1215" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B1215" s="13" t="s">
+      <c r="B1215" s="9" t="s">
         <v>1317</v>
       </c>
       <c r="C1215" t="s">
@@ -21602,7 +21602,7 @@
       <c r="A1216" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B1216" s="13" t="s">
+      <c r="B1216" s="9" t="s">
         <v>1317</v>
       </c>
       <c r="C1216" t="s">
@@ -21612,28 +21612,70 @@
         <v>1345</v>
       </c>
     </row>
+    <row r="1217" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1217" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1217" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>575</v>
+      </c>
+      <c r="D1217" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1218" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1218" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>349</v>
+      </c>
+      <c r="D1218" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1219" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1219" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>575</v>
+      </c>
+      <c r="D1219" t="s">
+        <v>1348</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D1216" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:D1219" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D1209">
       <sortCondition ref="C1:C1209"/>
     </sortState>
   </autoFilter>
+  <conditionalFormatting sqref="A1:A575 A579:A1219">
+    <cfRule type="duplicateValues" dxfId="11" priority="421"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A1219">
+    <cfRule type="duplicateValues" dxfId="10" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="427"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="428"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="429"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A637:A647">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A659:A661">
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A575 A579:A1216">
-    <cfRule type="duplicateValues" dxfId="9" priority="421"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1216">
-    <cfRule type="duplicateValues" dxfId="8" priority="424"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="425"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="426"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="427"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="428"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1216">
     <cfRule type="duplicateValues" dxfId="2" priority="436"/>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503E35DD-DBCC-4DC9-9732-A5DFA9DC8091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658480FE-3EE9-4D4C-A658-155AE863CAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1220</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4876" uniqueCount="1349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4880" uniqueCount="1350">
   <si>
     <t>VINH</t>
   </si>
@@ -4075,6 +4075,9 @@
   </si>
   <si>
     <t>00306-CO-OPXTRA PHAM VAN DONG</t>
+  </si>
+  <si>
+    <t>CF LE VAN CHI</t>
   </si>
 </sst>
 </file>
@@ -4104,12 +4107,18 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -4150,7 +4159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4178,6 +4187,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4579,7 +4597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1219"/>
+  <dimension ref="A1:D1220"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -21585,85 +21603,99 @@
       </c>
     </row>
     <row r="1215" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1215" s="1" t="s">
+      <c r="A1215" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="B1215" s="9" t="s">
-        <v>1317</v>
-      </c>
-      <c r="C1215" t="s">
+      <c r="B1215" s="12" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C1215" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="D1215" t="s">
+      <c r="D1215" s="13" t="s">
         <v>1344</v>
       </c>
     </row>
     <row r="1216" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1216" s="1" t="s">
+      <c r="A1216" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="B1216" s="9" t="s">
-        <v>1317</v>
-      </c>
-      <c r="C1216" t="s">
+      <c r="B1216" s="12" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C1216" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="D1216" t="s">
+      <c r="D1216" s="13" t="s">
         <v>1345</v>
       </c>
     </row>
     <row r="1217" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1217" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1217" s="10" t="s">
+      <c r="A1217" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1217" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C1217" t="s">
+      <c r="C1217" s="13" t="s">
         <v>575</v>
       </c>
-      <c r="D1217" t="s">
+      <c r="D1217" s="13" t="s">
         <v>1346</v>
       </c>
     </row>
     <row r="1218" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1218" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1218" s="10" t="s">
+      <c r="A1218" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1218" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C1218" t="s">
+      <c r="C1218" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="D1218" t="s">
+      <c r="D1218" s="13" t="s">
         <v>1347</v>
       </c>
     </row>
     <row r="1219" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1219" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1219" s="10" t="s">
+      <c r="A1219" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1219" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C1219" t="s">
+      <c r="C1219" s="13" t="s">
         <v>575</v>
       </c>
-      <c r="D1219" t="s">
+      <c r="D1219" s="13" t="s">
         <v>1348</v>
       </c>
     </row>
+    <row r="1220" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1220" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1220" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1220" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1220" s="13" t="s">
+        <v>1349</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D1219" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:D1220" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D1209">
       <sortCondition ref="C1:C1209"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="A1:A575 A579:A1219">
+  <conditionalFormatting sqref="A1:A575 A579:A1220">
     <cfRule type="duplicateValues" dxfId="11" priority="421"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1219">
+  <conditionalFormatting sqref="A1:A1220">
     <cfRule type="duplicateValues" dxfId="10" priority="424"/>
     <cfRule type="duplicateValues" dxfId="9" priority="425"/>
     <cfRule type="duplicateValues" dxfId="8" priority="426"/>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658480FE-3EE9-4D4C-A658-155AE863CAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8973E09-4E24-4E3B-9F75-BE798FC46BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4880" uniqueCount="1350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4888" uniqueCount="1352">
   <si>
     <t>VINH</t>
   </si>
@@ -4077,14 +4077,20 @@
     <t>00306-CO-OPXTRA PHAM VAN DONG</t>
   </si>
   <si>
-    <t>CF LE VAN CHI</t>
+    <t>02223-CF KDC VUON LAI 53</t>
+  </si>
+  <si>
+    <t>02224-CF TAN KY TAN QUY</t>
+  </si>
+  <si>
+    <t>02215-CF NGO CHI QUOC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4106,6 +4112,12 @@
       <name val="GMV Linotte"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -4121,7 +4133,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -4155,11 +4167,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4196,11 +4223,150 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C6500"/>
@@ -4597,7 +4763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1220"/>
+  <dimension ref="A1:D1223"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -21630,45 +21796,45 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="1217" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1217" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1217" s="14" t="s">
+    <row r="1217" spans="1:4" s="19" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1217" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1217" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="C1217" s="13" t="s">
+      <c r="C1217" s="19" t="s">
         <v>575</v>
       </c>
-      <c r="D1217" s="13" t="s">
+      <c r="D1217" s="19" t="s">
         <v>1346</v>
       </c>
     </row>
-    <row r="1218" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1218" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1218" s="14" t="s">
+    <row r="1218" spans="1:4" s="19" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1218" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1218" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1218" s="13" t="s">
+      <c r="C1218" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="D1218" s="13" t="s">
+      <c r="D1218" s="19" t="s">
         <v>1347</v>
       </c>
     </row>
-    <row r="1219" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1219" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1219" s="14" t="s">
+    <row r="1219" spans="1:4" s="19" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1219" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1219" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1219" s="13" t="s">
+      <c r="C1219" s="19" t="s">
         <v>575</v>
       </c>
-      <c r="D1219" s="13" t="s">
+      <c r="D1219" s="19" t="s">
         <v>1348</v>
       </c>
     </row>
@@ -21680,11 +21846,42 @@
         <v>124</v>
       </c>
       <c r="C1220" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D1220" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="D1220" s="20" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1221" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1221" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1221" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="D1221" t="s">
         <v>1349</v>
       </c>
+    </row>
+    <row r="1222" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1222" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1222" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1222" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="D1222" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B1223" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1220" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -21692,27 +21889,30 @@
       <sortCondition ref="C1:C1209"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="A1:A575 A579:A1220">
-    <cfRule type="duplicateValues" dxfId="11" priority="421"/>
+  <conditionalFormatting sqref="A1:A575 A579:A1222">
+    <cfRule type="duplicateValues" dxfId="12" priority="422"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1220">
-    <cfRule type="duplicateValues" dxfId="10" priority="424"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="425"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="426"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="427"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="428"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="429"/>
+  <conditionalFormatting sqref="A1:A1222">
+    <cfRule type="duplicateValues" dxfId="11" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="427"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="428"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A637:A647">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A659:A661">
     <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A659:A661">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+  <conditionalFormatting sqref="B1:B1216">
+    <cfRule type="duplicateValues" dxfId="3" priority="437"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="438"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="439"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1216">
-    <cfRule type="duplicateValues" dxfId="2" priority="436"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="437"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="438"/>
+  <conditionalFormatting sqref="D1224:D1048576 D1:D1222">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B206649-F5A5-42A7-9B55-E30286FE0C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454FA8CA-F1ED-42C3-A8E7-E8F1E58D2C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454FA8CA-F1ED-42C3-A8E7-E8F1E58D2C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928F6974-C331-4FF5-B960-2854AEEFF332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1250</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5000" uniqueCount="1382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5004" uniqueCount="1383">
   <si>
     <t>VINH</t>
   </si>
@@ -4174,6 +4174,9 @@
   </si>
   <si>
     <t>02185-CO.OPFOOD KDC HIEP BINH</t>
+  </si>
+  <si>
+    <t>BHX 468 Pham Van Chieu</t>
   </si>
 </sst>
 </file>
@@ -4326,7 +4329,37 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="58">
+  <dxfs count="61">
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -22692,48 +22725,64 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="1251" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="D1251" s="16"/>
+    <row r="1251" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1251" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1251" s="8" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1251" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D1251" s="1" t="s">
+        <v>1382</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1220" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:D1250" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D1209">
       <sortCondition ref="C1:C1209"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A637:A647">
-    <cfRule type="duplicateValues" dxfId="30" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A659:A661">
-    <cfRule type="duplicateValues" dxfId="29" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1216">
-    <cfRule type="duplicateValues" dxfId="28" priority="440"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="441"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="445"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1252:D1048576 D1:D282 D1231 D284:D1229">
-    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
+  <conditionalFormatting sqref="D1:D282 D1231 D284:D1229 D1251:D1048576">
+    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1252:D1048576 D1:D1249">
-    <cfRule type="duplicateValues" dxfId="24" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1250 D1252:D1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A575 A579:A1250">
-    <cfRule type="duplicateValues" dxfId="22" priority="443"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1250">
-    <cfRule type="duplicateValues" dxfId="21" priority="446"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="447"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="448"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="449"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="450"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="451"/>
+  <conditionalFormatting sqref="D1:D1249 D1251:D1048576">
+    <cfRule type="duplicateValues" dxfId="27" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A575 A579:A1251">
+    <cfRule type="duplicateValues" dxfId="25" priority="446"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A1251">
+    <cfRule type="duplicateValues" dxfId="24" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="454"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1251">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928F6974-C331-4FF5-B960-2854AEEFF332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CE83EF-FF7D-4DB8-9815-5D22DBF37CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4329,7 +4329,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="61">
+  <dxfs count="47">
     <dxf>
       <font>
         <color rgb="FF9C6500"/>
@@ -4337,16 +4337,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4627,136 +4617,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -22159,10 +22019,10 @@
         <v>1341</v>
       </c>
       <c r="C1210" t="s">
+        <v>504</v>
+      </c>
+      <c r="D1210" t="s">
         <v>1335</v>
-      </c>
-      <c r="D1210" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="1211" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22173,10 +22033,10 @@
         <v>1341</v>
       </c>
       <c r="C1211" t="s">
+        <v>545</v>
+      </c>
+      <c r="D1211" t="s">
         <v>1336</v>
-      </c>
-      <c r="D1211" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="1212" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22187,10 +22047,10 @@
         <v>1341</v>
       </c>
       <c r="C1212" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1212" t="s">
         <v>1337</v>
-      </c>
-      <c r="D1212" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="1213" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22201,10 +22061,10 @@
         <v>1341</v>
       </c>
       <c r="C1213" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1213" t="s">
         <v>1338</v>
-      </c>
-      <c r="D1213" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="1214" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22215,10 +22075,10 @@
         <v>1341</v>
       </c>
       <c r="C1214" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D1214" t="s">
         <v>1339</v>
-      </c>
-      <c r="D1214" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="1215" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22746,38 +22606,35 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A637:A647">
-    <cfRule type="duplicateValues" dxfId="33" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A659:A661">
-    <cfRule type="duplicateValues" dxfId="32" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1216">
-    <cfRule type="duplicateValues" dxfId="31" priority="443"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="444"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="445"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D282 D1231 D284:D1229 D1251:D1048576">
-    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
+  <conditionalFormatting sqref="D1:D282 D1231 D284:D1209 D1215:D1229 C1210:C1214 D1251:D1048576">
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1249 D1251:D1048576">
-    <cfRule type="duplicateValues" dxfId="27" priority="6"/>
+  <conditionalFormatting sqref="D1:D1209 D1215:D1249 C1210:C1214 D1251:D1048576">
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="26" priority="5"/>
+  <conditionalFormatting sqref="D1:D1209 D1215:D1048576 C1210:C1214">
+    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A575 A579:A1251">
-    <cfRule type="duplicateValues" dxfId="25" priority="446"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="446"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1251">
-    <cfRule type="duplicateValues" dxfId="24" priority="449"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="450"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="451"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="452"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="453"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="454"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1251">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CE83EF-FF7D-4DB8-9815-5D22DBF37CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F3DBDB-55FB-4880-974F-FA668A793FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5004" uniqueCount="1383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5012" uniqueCount="1385">
   <si>
     <t>VINH</t>
   </si>
@@ -4177,6 +4177,12 @@
   </si>
   <si>
     <t>BHX 468 Pham Van Chieu</t>
+  </si>
+  <si>
+    <t>BS Mart An Phu</t>
+  </si>
+  <si>
+    <t>02085-CO.OPFOOD PHAN VAN HON 285</t>
   </si>
 </sst>
 </file>
@@ -4279,7 +4285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4325,11 +4331,42 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="36">
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C6500"/>
@@ -4660,146 +4697,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -5076,7 +4973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1251"/>
+  <dimension ref="A1:D1253"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -22599,6 +22496,34 @@
         <v>1382</v>
       </c>
     </row>
+    <row r="1252" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1252" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1252" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>324</v>
+      </c>
+      <c r="D1252" s="1" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1253" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1253" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>1384</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D1250" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D1209">
@@ -22606,37 +22531,42 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A637:A647">
-    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A659:A661">
-    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1216">
-    <cfRule type="duplicateValues" dxfId="15" priority="443"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="444"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="446"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D282 D1231 D284:D1209 D1215:D1229 C1210:C1214 D1251:D1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1209 D1215:D1249 C1210:C1214 D1251:D1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1209 D1215:D1048576 C1210:C1214">
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+  <conditionalFormatting sqref="D1:D1209 C1210:C1214 D1215:D1048576">
+    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A575 A579:A1251">
-    <cfRule type="duplicateValues" dxfId="9" priority="446"/>
+  <conditionalFormatting sqref="A1:A575 A579:A1253">
+    <cfRule type="duplicateValues" dxfId="12" priority="449"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1251">
-    <cfRule type="duplicateValues" dxfId="8" priority="449"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="450"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="451"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="452"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="453"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="454"/>
+  <conditionalFormatting sqref="A1:A1253">
+    <cfRule type="duplicateValues" dxfId="11" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="454"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1251">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1252">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F3DBDB-55FB-4880-974F-FA668A793FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA211DC2-9A38-4D77-B675-D8CCDAA96270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1378</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5012" uniqueCount="1385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5512" uniqueCount="1511">
   <si>
     <t>VINH</t>
   </si>
@@ -4183,6 +4183,384 @@
   </si>
   <si>
     <t>02085-CO.OPFOOD PHAN VAN HON 285</t>
+  </si>
+  <si>
+    <t>CH00307-CO.OPSMILE  91 DINH TIEN HOANG</t>
+  </si>
+  <si>
+    <t>CH00308-CO.OPSMILE  201 NGUYEN XI</t>
+  </si>
+  <si>
+    <t>CH00312-CO.OPSMILE 389 AU CO</t>
+  </si>
+  <si>
+    <t>CH00313-CO.OPSMILE 22 PHONG PHU</t>
+  </si>
+  <si>
+    <t>CH00314-CO.OPSMILE 52 LY THUONG KIET</t>
+  </si>
+  <si>
+    <t>CH00315-CO.OPSMILE 106I LAC LONG QUAN</t>
+  </si>
+  <si>
+    <t>CH00316-CO.OPSMILE 175 TRAN VAN DANG</t>
+  </si>
+  <si>
+    <t>CH00317-CO.OPSMILE 606 BA THANG HAI</t>
+  </si>
+  <si>
+    <t>CH00319-CHEERS AN PHU SPORT</t>
+  </si>
+  <si>
+    <t>CH00320-CO.OPSMILE 123A TAM DANH</t>
+  </si>
+  <si>
+    <t>CH00321-CO.OPSMILE 50 LE VAN VIET</t>
+  </si>
+  <si>
+    <t>CH00322-CO.OPSMILE 41 LO SIEU</t>
+  </si>
+  <si>
+    <t>CH00328-CO.OPSMILE - 41 BANH VAN TRAN</t>
+  </si>
+  <si>
+    <t>CH00329-CO.OPSMILE - 248 NGUYEN THAI BINH</t>
+  </si>
+  <si>
+    <t>CH00335-CO.OPSMILE - 6 NGUYEN BINH KHIEM</t>
+  </si>
+  <si>
+    <t>CH00336-CO.OPSMILE - 631A CACH MANG THANG TAM</t>
+  </si>
+  <si>
+    <t>CH00337-CO.OPSMILE - 9 DUONG 9</t>
+  </si>
+  <si>
+    <t>CH00338-CO.OPSMILE - 149E DOI CUNG</t>
+  </si>
+  <si>
+    <t>CH00018-CO.OPSMILE CHO NGUYEN VAN TROI</t>
+  </si>
+  <si>
+    <t>CH00024-CO.OPSMILE CAO OC KHANG GIA</t>
+  </si>
+  <si>
+    <t>CH00042-CO.OPSMILE CHUNG CU THAI AN</t>
+  </si>
+  <si>
+    <t>CH00009-CO.OPSMILE 173 PHO CO DIEU</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>CH00033-CO.OPSMILE 43 DE THAM</t>
+  </si>
+  <si>
+    <t>CH00039-CO.OPSMILE 99 LAC LONG QUAN</t>
+  </si>
+  <si>
+    <t>CH00046-CO.OPSMILE 156 TRAN HUNG DAO</t>
+  </si>
+  <si>
+    <t>CH00048-CO.OPSMILE 7 DO NHUAN</t>
+  </si>
+  <si>
+    <t>CH00067-CO.OPSMILE 52 NGUYEN VAN DUNG</t>
+  </si>
+  <si>
+    <t>CH00109-CO.OPSMILE 112 BUI QUANG LA</t>
+  </si>
+  <si>
+    <t>CH00113-CO.OPSMILE 15B TRAN BINH TRONG</t>
+  </si>
+  <si>
+    <t>CH00118-CO.OPSMILE 80 THANH XUAN 13</t>
+  </si>
+  <si>
+    <t>CH00124-CO.OPSMILE 97 PHU CHAU</t>
+  </si>
+  <si>
+    <t>CH00125-CO.OPSMILE 424 NGUYEN DINH CHIEU</t>
+  </si>
+  <si>
+    <t>CH00126-CO.OPSMILE CU XA DO THANH</t>
+  </si>
+  <si>
+    <t>CH00127-CO.OPSMILE 380 NAM KY KHOI NGHIA</t>
+  </si>
+  <si>
+    <t>CH00129-CO.OPSMILE 29 VU HUY TAN</t>
+  </si>
+  <si>
+    <t>CH00130-CO.OPSMILE 284 LY THUONG KIET</t>
+  </si>
+  <si>
+    <t>CH00132-CO.OPSMILE 71 TRAN KE XUONG</t>
+  </si>
+  <si>
+    <t>CH00136-CO.OPSMILE 42 HOANG HOA THAM</t>
+  </si>
+  <si>
+    <t>CH00140-CO.OPSMILE 49 DUONG SO 7</t>
+  </si>
+  <si>
+    <t>CH00144-CO.OPSMILE 599 DIEN BIEN PHU</t>
+  </si>
+  <si>
+    <t>CH00145-CO.OPSMILE 69 NGUYEN GIA TRI</t>
+  </si>
+  <si>
+    <t>CH00148-CO.OPSMILE 687 XO VIET NGHE TINH</t>
+  </si>
+  <si>
+    <t>CH00149-CO.OPSMILE 69 LY THUONG KIET</t>
+  </si>
+  <si>
+    <t>CH00152-CO.OPSMILE 47 TRINH DINH TRONG</t>
+  </si>
+  <si>
+    <t>CH00153-CO.OPSMILE 38 NGUYEN CANH CHAN</t>
+  </si>
+  <si>
+    <t>CH00154-CO.OPSMILE 72 DO TAN PHONG</t>
+  </si>
+  <si>
+    <t>CH00155-CO.OPSMILE 312 QUANG TRUNG</t>
+  </si>
+  <si>
+    <t>CH00156-CO.OPSMILE 656 QUANG TRUNG</t>
+  </si>
+  <si>
+    <t>CH00157-CO.OPSMILE 10 LE THI HONG</t>
+  </si>
+  <si>
+    <t>CH00159-CO.OPSMILE 416 DUONG QUANG HAM</t>
+  </si>
+  <si>
+    <t>CH00161-CO.OPSMILE 30 DUONG SO 3</t>
+  </si>
+  <si>
+    <t>CH00163-CO.OPSMILE 18 NGUYEN THANH TUYEN</t>
+  </si>
+  <si>
+    <t>CH00166-CO.OPSMILE 729 NGUYEN KIEM</t>
+  </si>
+  <si>
+    <t>CH00168-CO.OPSMILE 311 DUONG H</t>
+  </si>
+  <si>
+    <t>CH00169-CO.OPSMILE 119 TRAN VAN KY</t>
+  </si>
+  <si>
+    <t>CH00171-CO.OPSMILE 198 DAT THANH</t>
+  </si>
+  <si>
+    <t>CH00172-CO.OPSMILE 125 BUI DINH TUY</t>
+  </si>
+  <si>
+    <t>CH00173-CO.OPSMILE 37 TRAN MAI NINH</t>
+  </si>
+  <si>
+    <t>CH00175-CO.OPSMILE 57 TRAN BINH TRONG</t>
+  </si>
+  <si>
+    <t>CH00176-CO.OPSMILE 3 THANH THAI</t>
+  </si>
+  <si>
+    <t>CH00177-CO.OPSMILE 27 DIEN BIEN PHU</t>
+  </si>
+  <si>
+    <t>CH00178-CO.OPSMILE 16 NGUYEN THIEN THUAT</t>
+  </si>
+  <si>
+    <t>CH00179-CO.OPSMILE 79 NGUYEN HONG</t>
+  </si>
+  <si>
+    <t>CH00181-CO.OPSMILE 113 TRAN KHAC CHAN</t>
+  </si>
+  <si>
+    <t>CH00183-CO.OPSMILE 300 NGUYEN VAN LINH</t>
+  </si>
+  <si>
+    <t>CH00186-CO.OPSMILE 60 LAM VAN BEN</t>
+  </si>
+  <si>
+    <t>CH00187-CO.OPSMILE 59 BUI DIEN</t>
+  </si>
+  <si>
+    <t>CH00194-CO.OPSMILE 48 NGUYEN CONG HOAN</t>
+  </si>
+  <si>
+    <t>CH00195-CO.OPSMILE 84 CAO THANG</t>
+  </si>
+  <si>
+    <t>CH00198-CO.OPSMILE 194 BACH DANG</t>
+  </si>
+  <si>
+    <t>CH00199-CO.OPSMILE 15 VO DUY NINH</t>
+  </si>
+  <si>
+    <t>CH00200-CO.OPSMILE 14 NGUYEN CUU VAN</t>
+  </si>
+  <si>
+    <t>CH00203-CO.OPSMILE 339 TO HIEN THANH</t>
+  </si>
+  <si>
+    <t>CH00204-CO.OPSMILE 58 CACH MANG THANG TAM</t>
+  </si>
+  <si>
+    <t>CH00205-CO.OPSMILE 445 NO TRANG LONG</t>
+  </si>
+  <si>
+    <t>CH00207-CO.OPSMILE 72 DUONG 17</t>
+  </si>
+  <si>
+    <t>CH00209-CO.OPSMILE 127 CO GIANG</t>
+  </si>
+  <si>
+    <t>CH00211-CO.OPSMILE 958 LAC LONG QUAN</t>
+  </si>
+  <si>
+    <t>CH00213-CO.OPSMILE 101 HUYNH MAN DAT</t>
+  </si>
+  <si>
+    <t>CH00214-CO.OPSMILE 91 TRAN QUANG DIEU</t>
+  </si>
+  <si>
+    <t>CH00215-CO.OPSMILE D48C NGUYEN TRAI</t>
+  </si>
+  <si>
+    <t>CH00216-CO.OPSMILE 35 BE VAN CAM</t>
+  </si>
+  <si>
+    <t>CH00219-CO.OPSMILE 63-65 BEN VAN DON</t>
+  </si>
+  <si>
+    <t>CH00222-CO.OPSMILE C2 TAY THANH</t>
+  </si>
+  <si>
+    <t>CH00223-CO.OPSMILE 144 AU CO</t>
+  </si>
+  <si>
+    <t>CH00224-CO.OPSMILE 220 XO VIET NGHE TINH</t>
+  </si>
+  <si>
+    <t>CH00226-CO.OPSMILE 197 PHUNG HUNG</t>
+  </si>
+  <si>
+    <t>CH00227-CO.OPSMILE 341 LAC LONG QUAN</t>
+  </si>
+  <si>
+    <t>CH00231-CO.OPSMILE 157 DUONG BA TRAC</t>
+  </si>
+  <si>
+    <t>CH00236-CO.OPSMILE 80 BA VAN</t>
+  </si>
+  <si>
+    <t>CH00238-CO.OPSMILE 654 LAC LONG QUAN</t>
+  </si>
+  <si>
+    <t>CH00239-CHEERS 307 LY TU TRONG</t>
+  </si>
+  <si>
+    <t>CH00240-CHEERS 45 PHAN CHU TRINH</t>
+  </si>
+  <si>
+    <t>CH00247-CHEERS 364 DIEN BIEN PHU</t>
+  </si>
+  <si>
+    <t>CH00250-CHEERS MOONLIGHT BOULEVARD</t>
+  </si>
+  <si>
+    <t>CH00251-CHEERS CARILLON 7</t>
+  </si>
+  <si>
+    <t>CH00257-CHEERS 135 TRAN HUNG DAO</t>
+  </si>
+  <si>
+    <t>CH00258-CO.OPSMILE GALAXY 9</t>
+  </si>
+  <si>
+    <t>CH00262-CO.OPSMILE 104 NGUYEN DINH CHIEU</t>
+  </si>
+  <si>
+    <t>CH00263-CO.OPSMILE 2 BAY HIEN</t>
+  </si>
+  <si>
+    <t>CH00264-CO.OPSMILE 50 TAN MY</t>
+  </si>
+  <si>
+    <t>CH00265-CO.OPSMILE 122ABC CACH MANG THANG 8</t>
+  </si>
+  <si>
+    <t>CH00273-CO.OPSMILE HUNG NGAN GARDEN</t>
+  </si>
+  <si>
+    <t>CH00274-CO.OPSMILE 85 TUE TINH</t>
+  </si>
+  <si>
+    <t>CH00275-CHEERS 236 VO VAN NGAN</t>
+  </si>
+  <si>
+    <t>CH00277-CO.OPSMILE 73 TO HIEU</t>
+  </si>
+  <si>
+    <t>CH00280-CO.OPSMILE 64 NGUYEN VAN THANH</t>
+  </si>
+  <si>
+    <t>CH00282-CO.OPSMILE - 23 DUONG SO 19</t>
+  </si>
+  <si>
+    <t>CH00285-CO.OPSMILE - D22 CU XA PHU LAM B</t>
+  </si>
+  <si>
+    <t>CH00286-CO.OPSMILE - 168A MINH PHUNG</t>
+  </si>
+  <si>
+    <t>CH00287-CO.OPSMILE - 160 NGUYEN TU GIAN</t>
+  </si>
+  <si>
+    <t>CH00288-CO.OPSMILE - 1245 NGUYEN DUY TRINH</t>
+  </si>
+  <si>
+    <t>CH00290-CO.OPSMILE - 111 THONG NHAT</t>
+  </si>
+  <si>
+    <t>CH00291-CO.OPSMILE - 260F PHAN ANH</t>
+  </si>
+  <si>
+    <t>CH00293-CHEERS - 22A CAO BA NHA</t>
+  </si>
+  <si>
+    <t>CH00294-CO.OPSMILE 377-379 HAN HAI NGUYEN</t>
+  </si>
+  <si>
+    <t>CH00295-CO.OPSMILE 326 DUONG BA TRAC</t>
+  </si>
+  <si>
+    <t>CH00296-CO.OPSMILE 71 DIEN BIEN PHU</t>
+  </si>
+  <si>
+    <t>CH00297-CO.OPSMILE 56 BAN CO</t>
+  </si>
+  <si>
+    <t>CH00298-CO.OPSMILE 157A NGUYEN SUY</t>
+  </si>
+  <si>
+    <t>CH00299-CO.OPSMILE 280 BUI HUU NGHIA</t>
+  </si>
+  <si>
+    <t>CH00300-CO.OPSMILE 710 PHAN VAN TRI</t>
+  </si>
+  <si>
+    <t>CH00303-CO.OPSMILE 209A BA HOM</t>
+  </si>
+  <si>
+    <t>CH00304-CO.OPSMILE 45 DUONG SO 9 CU XA BINH THOI</t>
+  </si>
+  <si>
+    <t>CH00305-CO.OPSMILE 1A1 KDC NGUYEN DINH CHIEU</t>
   </si>
 </sst>
 </file>
@@ -4285,7 +4663,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4321,7 +4699,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4331,12 +4708,71 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C6500"/>
@@ -4444,216 +4880,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4973,7 +5199,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1253"/>
+  <dimension ref="A1:D1378"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -8940,7 +9166,7 @@
       <c r="C283" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D283" s="16" t="s">
+      <c r="D283" s="15" t="s">
         <v>1380</v>
       </c>
     </row>
@@ -22100,7 +22326,7 @@
       <c r="C1223" t="s">
         <v>532</v>
       </c>
-      <c r="D1223" s="15" t="s">
+      <c r="D1223" t="s">
         <v>1351</v>
       </c>
     </row>
@@ -22114,7 +22340,7 @@
       <c r="C1224" t="s">
         <v>532</v>
       </c>
-      <c r="D1224" s="15" t="s">
+      <c r="D1224" t="s">
         <v>1353</v>
       </c>
     </row>
@@ -22268,7 +22494,7 @@
       <c r="C1235" t="s">
         <v>349</v>
       </c>
-      <c r="D1235" s="16" t="s">
+      <c r="D1235" s="15" t="s">
         <v>1364</v>
       </c>
     </row>
@@ -22282,7 +22508,7 @@
       <c r="C1236" t="s">
         <v>475</v>
       </c>
-      <c r="D1236" s="16" t="s">
+      <c r="D1236" s="15" t="s">
         <v>1365</v>
       </c>
     </row>
@@ -22296,7 +22522,7 @@
       <c r="C1237" t="s">
         <v>525</v>
       </c>
-      <c r="D1237" s="16" t="s">
+      <c r="D1237" s="15" t="s">
         <v>1366</v>
       </c>
     </row>
@@ -22310,7 +22536,7 @@
       <c r="C1238" t="s">
         <v>380</v>
       </c>
-      <c r="D1238" s="17" t="s">
+      <c r="D1238" s="16" t="s">
         <v>1367</v>
       </c>
     </row>
@@ -22324,7 +22550,7 @@
       <c r="C1239" t="s">
         <v>368</v>
       </c>
-      <c r="D1239" s="17" t="s">
+      <c r="D1239" s="16" t="s">
         <v>1368</v>
       </c>
     </row>
@@ -22338,7 +22564,7 @@
       <c r="C1240" t="s">
         <v>324</v>
       </c>
-      <c r="D1240" s="17" t="s">
+      <c r="D1240" s="16" t="s">
         <v>1369</v>
       </c>
     </row>
@@ -22352,7 +22578,7 @@
       <c r="C1241" t="s">
         <v>378</v>
       </c>
-      <c r="D1241" s="17" t="s">
+      <c r="D1241" s="16" t="s">
         <v>1370</v>
       </c>
     </row>
@@ -22366,7 +22592,7 @@
       <c r="C1242" t="s">
         <v>517</v>
       </c>
-      <c r="D1242" s="17" t="s">
+      <c r="D1242" s="16" t="s">
         <v>1371</v>
       </c>
     </row>
@@ -22380,7 +22606,7 @@
       <c r="C1243" t="s">
         <v>1373</v>
       </c>
-      <c r="D1243" s="18" t="s">
+      <c r="D1243" s="17" t="s">
         <v>1372</v>
       </c>
     </row>
@@ -22394,7 +22620,7 @@
       <c r="C1244" t="s">
         <v>525</v>
       </c>
-      <c r="D1244" s="18" t="s">
+      <c r="D1244" s="17" t="s">
         <v>1374</v>
       </c>
     </row>
@@ -22408,7 +22634,7 @@
       <c r="C1245" t="s">
         <v>358</v>
       </c>
-      <c r="D1245" s="18" t="s">
+      <c r="D1245" s="17" t="s">
         <v>1375</v>
       </c>
     </row>
@@ -22422,7 +22648,7 @@
       <c r="C1246" t="s">
         <v>370</v>
       </c>
-      <c r="D1246" s="16" t="s">
+      <c r="D1246" s="15" t="s">
         <v>1376</v>
       </c>
     </row>
@@ -22436,7 +22662,7 @@
       <c r="C1247" t="s">
         <v>571</v>
       </c>
-      <c r="D1247" s="18" t="s">
+      <c r="D1247" s="17" t="s">
         <v>1377</v>
       </c>
     </row>
@@ -22450,7 +22676,7 @@
       <c r="C1248" t="s">
         <v>339</v>
       </c>
-      <c r="D1248" s="18" t="s">
+      <c r="D1248" s="17" t="s">
         <v>1378</v>
       </c>
     </row>
@@ -22464,7 +22690,7 @@
       <c r="C1249" t="s">
         <v>409</v>
       </c>
-      <c r="D1249" s="18" t="s">
+      <c r="D1249" s="17" t="s">
         <v>1379</v>
       </c>
     </row>
@@ -22478,7 +22704,7 @@
       <c r="C1250" t="s">
         <v>349</v>
       </c>
-      <c r="D1250" s="16" t="s">
+      <c r="D1250" s="15" t="s">
         <v>1381</v>
       </c>
     </row>
@@ -22511,7 +22737,7 @@
       </c>
     </row>
     <row r="1253" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1253" s="19" t="s">
+      <c r="A1253" s="10" t="s">
         <v>337</v>
       </c>
       <c r="B1253" s="9" t="s">
@@ -22524,52 +22750,1802 @@
         <v>1384</v>
       </c>
     </row>
+    <row r="1254" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1254" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1254" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>363</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1255" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1255" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>573</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1256" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1256" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1256" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1257" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1257" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>551</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1258" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1258" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1258" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1259" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1259" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1260" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1260" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>369</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1261" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1261" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>560</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1262" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1262" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>368</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1263" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1263" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>409</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1264" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1264" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>409</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1265" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1265" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1266" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1266" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>462</v>
+      </c>
+      <c r="D1266" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1267" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1267" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>421</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1268" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1268" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>568</v>
+      </c>
+      <c r="D1268" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1269" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1269" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>462</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1270" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1270" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>471</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1271" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1271" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>409</v>
+      </c>
+      <c r="D1271" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1272" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1272" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1273" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1273" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1274" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1274" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>471</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1275" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1275" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>679</v>
+      </c>
+      <c r="D1275" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1276" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1276" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>363</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1277" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1277" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>371</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1278" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1278" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1279" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1279" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1279" t="s">
+        <v>475</v>
+      </c>
+      <c r="D1279" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1280" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1280" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1280" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1281" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1281" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1281" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1282" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1282" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>475</v>
+      </c>
+      <c r="D1282" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1283" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1283" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>532</v>
+      </c>
+      <c r="D1283" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1284" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1284" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1284" t="s">
+        <v>471</v>
+      </c>
+      <c r="D1284" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1285" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1285" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1285" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1286" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1286" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1286" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1287" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1287" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1287" t="s">
+        <v>537</v>
+      </c>
+      <c r="D1287" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1288" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1288" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1288" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1289" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1289" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1289" t="s">
+        <v>339</v>
+      </c>
+      <c r="D1289" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1290" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1290" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1290" t="s">
+        <v>572</v>
+      </c>
+      <c r="D1290" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1291" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1291" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1291" t="s">
+        <v>421</v>
+      </c>
+      <c r="D1291" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1292" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1292" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1292" t="s">
+        <v>462</v>
+      </c>
+      <c r="D1292" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1293" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1293" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>409</v>
+      </c>
+      <c r="D1293" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1294" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1294" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1294" t="s">
+        <v>369</v>
+      </c>
+      <c r="D1294" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1295" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1295" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>371</v>
+      </c>
+      <c r="D1295" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1296" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1296" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1296" t="s">
+        <v>382</v>
+      </c>
+      <c r="D1296" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1297" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1297" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>380</v>
+      </c>
+      <c r="D1297" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1298" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1298" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1298" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1298" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1299" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1299" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1299" t="s">
+        <v>568</v>
+      </c>
+      <c r="D1299" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1300" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1300" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1300" t="s">
+        <v>568</v>
+      </c>
+      <c r="D1300" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1301" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1301" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1301" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1301" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1302" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1302" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1302" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1303" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1303" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1303" t="s">
+        <v>462</v>
+      </c>
+      <c r="D1303" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1304" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1304" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1304" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1305" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1305" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1305" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1305" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1306" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1306" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1306" t="s">
+        <v>369</v>
+      </c>
+      <c r="D1306" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1307" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1307" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1307" t="s">
+        <v>382</v>
+      </c>
+      <c r="D1307" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1308" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1308" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1308" t="s">
+        <v>568</v>
+      </c>
+      <c r="D1308" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1309" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1309" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1309" t="s">
+        <v>537</v>
+      </c>
+      <c r="D1309" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1310" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1310" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1310" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1311" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1311" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>365</v>
+      </c>
+      <c r="D1311" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1312" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1312" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1312" t="s">
+        <v>363</v>
+      </c>
+      <c r="D1312" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1313" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1313" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1313" t="s">
+        <v>380</v>
+      </c>
+      <c r="D1313" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1314" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1314" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1314" t="s">
+        <v>518</v>
+      </c>
+      <c r="D1314" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1315" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1315" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>551</v>
+      </c>
+      <c r="D1315" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1316" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1316" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>537</v>
+      </c>
+      <c r="D1316" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1317" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1317" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1317" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1318" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1318" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1318" t="s">
+        <v>414</v>
+      </c>
+      <c r="D1318" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1319" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1319" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1319" t="s">
+        <v>679</v>
+      </c>
+      <c r="D1319" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1320" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1320" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1320" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1320" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1321" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1321" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1321" t="s">
+        <v>341</v>
+      </c>
+      <c r="D1321" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1322" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1322" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1322" t="s">
+        <v>537</v>
+      </c>
+      <c r="D1322" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1323" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1323" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1323" t="s">
+        <v>387</v>
+      </c>
+      <c r="D1323" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1324" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1324" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1324" t="s">
+        <v>387</v>
+      </c>
+      <c r="D1324" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1325" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1325" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>426</v>
+      </c>
+      <c r="D1325" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1326" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1326" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1326" t="s">
+        <v>504</v>
+      </c>
+      <c r="D1326" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1327" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1327" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1327" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1327" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1328" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1328" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>387</v>
+      </c>
+      <c r="D1328" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1329" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1329" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1329" t="s">
+        <v>379</v>
+      </c>
+      <c r="D1329" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1330" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1330" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>371</v>
+      </c>
+      <c r="D1330" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1331" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1331" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1331" t="s">
+        <v>339</v>
+      </c>
+      <c r="D1331" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1332" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1332" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1332" t="s">
+        <v>382</v>
+      </c>
+      <c r="D1332" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1333" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1333" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1333" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1333" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1334" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1334" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1334" t="s">
+        <v>565</v>
+      </c>
+      <c r="D1334" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1335" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1335" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1335" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1335" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1336" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1336" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1336" t="s">
+        <v>361</v>
+      </c>
+      <c r="D1336" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1337" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1337" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1337" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1337" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1338" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1338" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1338" t="s">
+        <v>574</v>
+      </c>
+      <c r="D1338" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1339" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1339" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1339" t="s">
+        <v>346</v>
+      </c>
+      <c r="D1339" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1340" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1340" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1340" t="s">
+        <v>375</v>
+      </c>
+      <c r="D1340" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1341" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1341" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1341" t="s">
+        <v>376</v>
+      </c>
+      <c r="D1341" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1342" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1342" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1342" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1342" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1343" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1343" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1343" t="s">
+        <v>367</v>
+      </c>
+      <c r="D1343" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1344" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1344" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1344" t="s">
+        <v>475</v>
+      </c>
+      <c r="D1344" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1345" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1345" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1345" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1345" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1346" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1346" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1346" t="s">
+        <v>363</v>
+      </c>
+      <c r="D1346" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1347" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1347" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1347" t="s">
+        <v>366</v>
+      </c>
+      <c r="D1347" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1348" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1348" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1348" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1348" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1349" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1349" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1349" t="s">
+        <v>462</v>
+      </c>
+      <c r="D1349" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1350" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1350" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1350" t="s">
+        <v>409</v>
+      </c>
+      <c r="D1350" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1351" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1351" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1351" t="s">
+        <v>380</v>
+      </c>
+      <c r="D1351" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1352" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1352" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1352" t="s">
+        <v>462</v>
+      </c>
+      <c r="D1352" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1353" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1353" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1353" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1353" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1354" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1354" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1354" t="s">
+        <v>375</v>
+      </c>
+      <c r="D1354" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1355" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1355" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1355" t="s">
+        <v>573</v>
+      </c>
+      <c r="D1355" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1356" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1356" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1356" t="s">
+        <v>384</v>
+      </c>
+      <c r="D1356" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1357" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1357" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1357" t="s">
+        <v>462</v>
+      </c>
+      <c r="D1357" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1358" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1358" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1358" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1358" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1359" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1359" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1359" t="s">
+        <v>537</v>
+      </c>
+      <c r="D1359" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1360" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1360" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1360" t="s">
+        <v>374</v>
+      </c>
+      <c r="D1360" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1361" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1361" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1361" t="s">
+        <v>339</v>
+      </c>
+      <c r="D1361" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1362" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1362" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1362" t="s">
+        <v>573</v>
+      </c>
+      <c r="D1362" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1363" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1363" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1363" t="s">
+        <v>365</v>
+      </c>
+      <c r="D1363" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1364" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1364" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1364" t="s">
+        <v>421</v>
+      </c>
+      <c r="D1364" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1365" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1365" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1365" t="s">
+        <v>324</v>
+      </c>
+      <c r="D1365" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1366" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1366" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1366" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1366" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1367" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1367" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1367" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1367" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1368" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1368" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1368" t="s">
+        <v>366</v>
+      </c>
+      <c r="D1368" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1369" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1369" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1369" t="s">
+        <v>540</v>
+      </c>
+      <c r="D1369" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1370" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1370" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1370" t="s">
+        <v>339</v>
+      </c>
+      <c r="D1370" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1371" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1371" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1371" t="s">
+        <v>471</v>
+      </c>
+      <c r="D1371" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1372" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1372" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1372" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1372" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1373" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1373" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1373" t="s">
+        <v>324</v>
+      </c>
+      <c r="D1373" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1374" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1374" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1374" t="s">
+        <v>573</v>
+      </c>
+      <c r="D1374" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1375" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1375" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1375" t="s">
+        <v>365</v>
+      </c>
+      <c r="D1375" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1376" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1376" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1376" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1376" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1377" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1377" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1377" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1377" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1378" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1378" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1378" t="s">
+        <v>366</v>
+      </c>
+      <c r="D1378" t="s">
+        <v>1406</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D1250" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:D1378" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D1209">
       <sortCondition ref="C1:C1209"/>
     </sortState>
   </autoFilter>
+  <conditionalFormatting sqref="A1:A575 A579:A1253">
+    <cfRule type="duplicateValues" dxfId="20" priority="449"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A1253">
+    <cfRule type="duplicateValues" dxfId="19" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="454"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="457"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A637:A647">
-    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A659:A661">
-    <cfRule type="duplicateValues" dxfId="19" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1216">
-    <cfRule type="duplicateValues" dxfId="18" priority="446"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="447"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="446"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="448"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1251">
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1252">
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D282 D1231 D284:D1209 D1215:D1229 C1210:C1214 D1251:D1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1209 C1210:C1214 D1215:D1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1209 D1215:D1249 C1210:C1214 D1251:D1048576">
-    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1209 C1210:C1214 D1215:D1048576">
-    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A575 A579:A1253">
-    <cfRule type="duplicateValues" dxfId="12" priority="449"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1253">
-    <cfRule type="duplicateValues" dxfId="11" priority="452"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="453"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="454"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="455"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="456"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="457"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1251">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1252">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA211DC2-9A38-4D77-B675-D8CCDAA96270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92176E37-2687-40B6-B7A4-2431C128210D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5512" uniqueCount="1511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5516" uniqueCount="1512">
   <si>
     <t>VINH</t>
   </si>
@@ -4561,6 +4561,9 @@
   </si>
   <si>
     <t>CH00305-CO.OPSMILE 1A1 KDC NGUYEN DINH CHIEU</t>
+  </si>
+  <si>
+    <t>GS25 Vo Thanh Trang - Tan Binh</t>
   </si>
 </sst>
 </file>
@@ -5199,7 +5202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1378"/>
+  <dimension ref="A1:D1379"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -24498,6 +24501,20 @@
       </c>
       <c r="D1378" t="s">
         <v>1406</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1379" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1379" s="9" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C1379" t="s">
+        <v>339</v>
+      </c>
+      <c r="D1379" t="s">
+        <v>1511</v>
       </c>
     </row>
   </sheetData>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92176E37-2687-40B6-B7A4-2431C128210D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A09E04-923B-43B8-BC05-A37AA2ECE6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5516" uniqueCount="1512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5644" uniqueCount="1563">
   <si>
     <t>VINH</t>
   </si>
@@ -4564,6 +4564,159 @@
   </si>
   <si>
     <t>GS25 Vo Thanh Trang - Tan Binh</t>
+  </si>
+  <si>
+    <t>CH00221-CO.OPSMILE 75C CU XA PHU THO HOA</t>
+  </si>
+  <si>
+    <t>phuong Hoa Binh</t>
+  </si>
+  <si>
+    <t>CH00225-CO.OPSMILE 53 VO VAN NGAN</t>
+  </si>
+  <si>
+    <t>phuong Thu Duc</t>
+  </si>
+  <si>
+    <t>CH00228-CO.OPSMILE D80 KDC THOI AN</t>
+  </si>
+  <si>
+    <t>phuong Thoi An</t>
+  </si>
+  <si>
+    <t>CH00241-CHEERS DUONG 17A</t>
+  </si>
+  <si>
+    <t>phuong An Lac</t>
+  </si>
+  <si>
+    <t>CH00242-CHEERS BENH VIEN QUOC TE CITY</t>
+  </si>
+  <si>
+    <t>CH00244-CHEERS DAI HOC KINH TE BINH CHANH</t>
+  </si>
+  <si>
+    <t>xa Binh Hung</t>
+  </si>
+  <si>
+    <t>CH00245-CHEERS 1056A NGUYEN VAN LINH</t>
+  </si>
+  <si>
+    <t>phuong Tan Hung</t>
+  </si>
+  <si>
+    <t>CH00246-CHEERS THU THIEM DRAGON</t>
+  </si>
+  <si>
+    <t>phuong Cat Lai</t>
+  </si>
+  <si>
+    <t>CH00248-CHEERS RICHMOND</t>
+  </si>
+  <si>
+    <t>phuong Binh Thanh</t>
+  </si>
+  <si>
+    <t>CH00249-CHEERS MOONLIGHT PARK VIEW</t>
+  </si>
+  <si>
+    <t>CH00252-CHEERS KTX 43 NGUYEN CHI THANH</t>
+  </si>
+  <si>
+    <t>phuong An Dong</t>
+  </si>
+  <si>
+    <t>CH00256-CHEERS GIGAMALL</t>
+  </si>
+  <si>
+    <t>phuong Hiep Binh</t>
+  </si>
+  <si>
+    <t>CH00259-CO.OPSMILE JAMILA PHU HUU</t>
+  </si>
+  <si>
+    <t>phuong Long Truong</t>
+  </si>
+  <si>
+    <t>CH00260-CO.OPSMILE Q7 SAIGON COMPLEX</t>
+  </si>
+  <si>
+    <t>phuong Phu Thuan</t>
+  </si>
+  <si>
+    <t>CH00266-CHEERS LAVITA GARDEN</t>
+  </si>
+  <si>
+    <t>CH00269-CO.OPSMILE SATURN Q7 SAIGON COMPLEX</t>
+  </si>
+  <si>
+    <t>CH00272-CO.OPSMILE D1 TECCO TOWN</t>
+  </si>
+  <si>
+    <t>phuong Tan Tao</t>
+  </si>
+  <si>
+    <t>CH00283-CO.OPSMILE - RICCA PHU HUU</t>
+  </si>
+  <si>
+    <t>CH00284-CO.OPSMILE - 85 TAN THOI NHAT 8</t>
+  </si>
+  <si>
+    <t>phuong Dong Hung Thuan</t>
+  </si>
+  <si>
+    <t>CH00289-CO.OPSMILE - 36 DUONG 63</t>
+  </si>
+  <si>
+    <t>phuong Binh Trung</t>
+  </si>
+  <si>
+    <t>CH00292-CO.OPSMILE - 105 DUONG DINH HOI</t>
+  </si>
+  <si>
+    <t>phuong Phuoc Long</t>
+  </si>
+  <si>
+    <t>CH00301-CO.OPSMILE CHUONG DUONG HOME</t>
+  </si>
+  <si>
+    <t>CH00302-CO.OPSMILE 52 DUONG SO 3</t>
+  </si>
+  <si>
+    <t>phuong Binh Hung Hoa</t>
+  </si>
+  <si>
+    <t>CH00306-CO.OPSMILE 63 DUONG SO 5</t>
+  </si>
+  <si>
+    <t>CH00309-CO.OPSMILE SON KY 1</t>
+  </si>
+  <si>
+    <t>phuong Tay Thanh</t>
+  </si>
+  <si>
+    <t>CH00310-CO.OPSMILE  8 DUONG 102</t>
+  </si>
+  <si>
+    <t>phuong Tang Nhon Phu</t>
+  </si>
+  <si>
+    <t>CH00318-CHEERS THE PRIVIA KHANG DIEN</t>
+  </si>
+  <si>
+    <t>CH00323-CO.OPSMILE 793 TRAN XUAN SOAN</t>
+  </si>
+  <si>
+    <t>CH00324-CO.OPSMILE 258 DUONG BA TRAC</t>
+  </si>
+  <si>
+    <t>CH00325-CO.OPSMILE - 1NH DUONG SO 14A</t>
+  </si>
+  <si>
+    <t>CH00326-CO.OPSMILE - 33 NGUYEN DINH KHOI</t>
+  </si>
+  <si>
+    <t>CH00327-CO.OPSMILE - 126 VU TUNG</t>
   </si>
 </sst>
 </file>
@@ -5202,7 +5355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1379"/>
+  <dimension ref="A1:D1411"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -24515,6 +24668,454 @@
       </c>
       <c r="D1379" t="s">
         <v>1511</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1380" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1380" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1380" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D1380" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1381" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1381" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1381" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D1381" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1382" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1382" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D1382" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1383" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1383" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1383" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D1383" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1384" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1384" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1384" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D1384" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1385" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1385" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1385" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D1385" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1386" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1386" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1386" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D1386" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1387" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1387" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D1387" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1388" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1388" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D1388" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1389" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1389" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D1389" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1390" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1390" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D1390" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1391" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1391" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D1391" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1392" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1392" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1392" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1393" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1393" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D1393" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1394" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1394" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D1394" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1395" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1395" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D1395" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1396" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1396" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D1396" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1397" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1397" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1397" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1398" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1398" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D1398" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1399" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1399" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D1399" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1400" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1400" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D1400" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1401" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1401" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D1401" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1402" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1402" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D1402" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1403" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1403" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D1403" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1404" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1404" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D1404" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1405" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1405" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D1405" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1406" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1406" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D1406" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1407" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1407" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>380</v>
+      </c>
+      <c r="D1407" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1408" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1408" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1408" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1409" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1409" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>382</v>
+      </c>
+      <c r="D1409" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1410" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1410" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1410" t="s">
+        <v>540</v>
+      </c>
+      <c r="D1410" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1411" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1411" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>462</v>
+      </c>
+      <c r="D1411" t="s">
+        <v>1562</v>
       </c>
     </row>
   </sheetData>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A09E04-923B-43B8-BC05-A37AA2ECE6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C4FBA2-4DE8-45E8-823A-BB1C7906B353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5644" uniqueCount="1563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5648" uniqueCount="1564">
   <si>
     <t>VINH</t>
   </si>
@@ -4717,6 +4717,9 @@
   </si>
   <si>
     <t>CH00327-CO.OPSMILE - 126 VU TUNG</t>
+  </si>
+  <si>
+    <t>BHX CITYLAND DS8</t>
   </si>
 </sst>
 </file>
@@ -5355,7 +5358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1411"/>
+  <dimension ref="A1:D1412"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -25116,6 +25119,20 @@
       </c>
       <c r="D1411" t="s">
         <v>1562</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1412" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1412" s="9" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1412" t="s">
+        <v>1563</v>
       </c>
     </row>
   </sheetData>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C4FBA2-4DE8-45E8-823A-BB1C7906B353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B2725B-2421-48EA-98C8-7543B0326C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5648" uniqueCount="1564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5652" uniqueCount="1565">
   <si>
     <t>VINH</t>
   </si>
@@ -4720,13 +4720,19 @@
   </si>
   <si>
     <t>BHX CITYLAND DS8</t>
+  </si>
+  <si>
+    <t>CH00261-CO.OPSMILE CITY LAND</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4750,6 +4756,13 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4819,10 +4832,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4867,11 +4881,255 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="45">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5358,7 +5616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1412"/>
+  <dimension ref="A1:D1413"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -25135,6 +25393,20 @@
         <v>1563</v>
       </c>
     </row>
+    <row r="1413" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1413" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1413" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1413" s="18" t="s">
+        <v>1564</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D1378" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D1209">
@@ -25142,45 +25414,51 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:A575 A579:A1253">
-    <cfRule type="duplicateValues" dxfId="20" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1253">
-    <cfRule type="duplicateValues" dxfId="19" priority="452"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="453"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="454"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="455"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="456"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="454"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="458"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="459"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A637:A647">
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A659:A661">
-    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1216">
-    <cfRule type="duplicateValues" dxfId="11" priority="446"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="447"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1251">
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1252">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D282 D1231 D284:D1209 D1215:D1229 C1210:C1214 D1251:D1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
+  <conditionalFormatting sqref="D1:D282 D1231 D284:D1209 D1215:D1229 C1210:C1214 D1251:D1412 D1414:D1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1209 C1210:C1214 D1215:D1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+  <conditionalFormatting sqref="D1:D1209 C1210:C1214 D1215:D1412 D1414:D1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1209 D1215:D1249 C1210:C1214 D1251:D1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  <conditionalFormatting sqref="D1:D1209 D1215:D1249 C1210:C1214 D1251:D1412 D1414:D1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1413">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B2725B-2421-48EA-98C8-7543B0326C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BB8D8A-0168-4D11-BC9C-8016EF0F51E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5652" uniqueCount="1565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5656" uniqueCount="1565">
   <si>
     <t>VINH</t>
   </si>
@@ -4086,9 +4086,6 @@
     <t>GS25 YEN THE</t>
   </si>
   <si>
-    <t>GS25</t>
-  </si>
-  <si>
     <t>GS25 LAM SON</t>
   </si>
   <si>
@@ -4723,6 +4720,9 @@
   </si>
   <si>
     <t>CH00261-CO.OPSMILE CITY LAND</t>
+  </si>
+  <si>
+    <t>BHX CU XA DO THANH</t>
   </si>
 </sst>
 </file>
@@ -5616,7 +5616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1413"/>
+  <dimension ref="A1:D1414"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -9584,7 +9584,7 @@
         <v>332</v>
       </c>
       <c r="D283" s="15" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22738,7 +22738,7 @@
         <v>337</v>
       </c>
       <c r="B1223" s="9" t="s">
-        <v>1352</v>
+        <v>18</v>
       </c>
       <c r="C1223" t="s">
         <v>532</v>
@@ -22752,13 +22752,13 @@
         <v>337</v>
       </c>
       <c r="B1224" s="9" t="s">
-        <v>1352</v>
+        <v>18</v>
       </c>
       <c r="C1224" t="s">
         <v>532</v>
       </c>
       <c r="D1224" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="1225" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22772,7 +22772,7 @@
         <v>560</v>
       </c>
       <c r="D1225" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="1226" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22786,7 +22786,7 @@
         <v>567</v>
       </c>
       <c r="D1226" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="1227" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22800,7 +22800,7 @@
         <v>498</v>
       </c>
       <c r="D1227" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="1228" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22814,7 +22814,7 @@
         <v>369</v>
       </c>
       <c r="D1228" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="1229" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22828,7 +22828,7 @@
         <v>532</v>
       </c>
       <c r="D1229" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="1230" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22842,7 +22842,7 @@
         <v>567</v>
       </c>
       <c r="D1230" s="14" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="1231" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22856,7 +22856,7 @@
         <v>504</v>
       </c>
       <c r="D1231" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="1232" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22870,7 +22870,7 @@
         <v>563</v>
       </c>
       <c r="D1232" s="14" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="1233" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22884,7 +22884,7 @@
         <v>504</v>
       </c>
       <c r="D1233" s="14" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="1234" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22898,7 +22898,7 @@
         <v>563</v>
       </c>
       <c r="D1234" s="14" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="1235" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22912,7 +22912,7 @@
         <v>349</v>
       </c>
       <c r="D1235" s="15" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="1236" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22926,7 +22926,7 @@
         <v>475</v>
       </c>
       <c r="D1236" s="15" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="1237" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22940,7 +22940,7 @@
         <v>525</v>
       </c>
       <c r="D1237" s="15" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="1238" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22954,7 +22954,7 @@
         <v>380</v>
       </c>
       <c r="D1238" s="16" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="1239" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22968,7 +22968,7 @@
         <v>368</v>
       </c>
       <c r="D1239" s="16" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="1240" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22982,7 +22982,7 @@
         <v>324</v>
       </c>
       <c r="D1240" s="16" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="1241" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -22996,7 +22996,7 @@
         <v>378</v>
       </c>
       <c r="D1241" s="16" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="1242" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -23010,7 +23010,7 @@
         <v>517</v>
       </c>
       <c r="D1242" s="16" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="1243" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -23021,10 +23021,10 @@
         <v>124</v>
       </c>
       <c r="C1243" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D1243" s="17" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="1244" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -23038,7 +23038,7 @@
         <v>525</v>
       </c>
       <c r="D1244" s="17" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="1245" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -23052,7 +23052,7 @@
         <v>358</v>
       </c>
       <c r="D1245" s="17" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="1246" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -23066,7 +23066,7 @@
         <v>370</v>
       </c>
       <c r="D1246" s="15" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="1247" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -23080,7 +23080,7 @@
         <v>571</v>
       </c>
       <c r="D1247" s="17" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="1248" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -23094,7 +23094,7 @@
         <v>339</v>
       </c>
       <c r="D1248" s="17" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="1249" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -23108,7 +23108,7 @@
         <v>409</v>
       </c>
       <c r="D1249" s="17" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="1250" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -23122,7 +23122,7 @@
         <v>349</v>
       </c>
       <c r="D1250" s="15" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="1251" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -23136,7 +23136,7 @@
         <v>475</v>
       </c>
       <c r="D1251" s="1" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="1252" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -23150,7 +23150,7 @@
         <v>324</v>
       </c>
       <c r="D1252" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="1253" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -23161,10 +23161,10 @@
         <v>124</v>
       </c>
       <c r="C1253" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D1253" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="1254" spans="1:4" x14ac:dyDescent="0.2">
@@ -23172,13 +23172,13 @@
         <v>327</v>
       </c>
       <c r="B1254" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1254" t="s">
         <v>363</v>
       </c>
       <c r="D1254" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="1255" spans="1:4" x14ac:dyDescent="0.2">
@@ -23186,13 +23186,13 @@
         <v>327</v>
       </c>
       <c r="B1255" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1255" t="s">
         <v>573</v>
       </c>
       <c r="D1255" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="1256" spans="1:4" x14ac:dyDescent="0.2">
@@ -23200,13 +23200,13 @@
         <v>327</v>
       </c>
       <c r="B1256" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1256" t="s">
         <v>416</v>
       </c>
       <c r="D1256" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="1257" spans="1:4" x14ac:dyDescent="0.2">
@@ -23214,13 +23214,13 @@
         <v>337</v>
       </c>
       <c r="B1257" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1257" t="s">
         <v>551</v>
       </c>
       <c r="D1257" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="1258" spans="1:4" x14ac:dyDescent="0.2">
@@ -23228,13 +23228,13 @@
         <v>327</v>
       </c>
       <c r="B1258" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1258" t="s">
         <v>416</v>
       </c>
       <c r="D1258" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="1259" spans="1:4" x14ac:dyDescent="0.2">
@@ -23242,13 +23242,13 @@
         <v>320</v>
       </c>
       <c r="B1259" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1259" t="s">
         <v>325</v>
       </c>
       <c r="D1259" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="1260" spans="1:4" x14ac:dyDescent="0.2">
@@ -23256,13 +23256,13 @@
         <v>320</v>
       </c>
       <c r="B1260" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1260" t="s">
         <v>369</v>
       </c>
       <c r="D1260" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="1261" spans="1:4" x14ac:dyDescent="0.2">
@@ -23270,13 +23270,13 @@
         <v>337</v>
       </c>
       <c r="B1261" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1261" t="s">
         <v>560</v>
       </c>
       <c r="D1261" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="1262" spans="1:4" x14ac:dyDescent="0.2">
@@ -23284,13 +23284,13 @@
         <v>1</v>
       </c>
       <c r="B1262" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1262" t="s">
         <v>368</v>
       </c>
       <c r="D1262" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="1263" spans="1:4" x14ac:dyDescent="0.2">
@@ -23298,13 +23298,13 @@
         <v>327</v>
       </c>
       <c r="B1263" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1263" t="s">
         <v>409</v>
       </c>
       <c r="D1263" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="1264" spans="1:4" x14ac:dyDescent="0.2">
@@ -23312,13 +23312,13 @@
         <v>327</v>
       </c>
       <c r="B1264" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1264" t="s">
         <v>409</v>
       </c>
       <c r="D1264" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="1265" spans="1:4" x14ac:dyDescent="0.2">
@@ -23326,13 +23326,13 @@
         <v>327</v>
       </c>
       <c r="B1265" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1265" t="s">
         <v>364</v>
       </c>
       <c r="D1265" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="1266" spans="1:4" x14ac:dyDescent="0.2">
@@ -23340,13 +23340,13 @@
         <v>320</v>
       </c>
       <c r="B1266" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1266" t="s">
         <v>462</v>
       </c>
       <c r="D1266" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="1267" spans="1:4" x14ac:dyDescent="0.2">
@@ -23354,13 +23354,13 @@
         <v>327</v>
       </c>
       <c r="B1267" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1267" t="s">
         <v>421</v>
       </c>
       <c r="D1267" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="1268" spans="1:4" x14ac:dyDescent="0.2">
@@ -23368,13 +23368,13 @@
         <v>1</v>
       </c>
       <c r="B1268" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1268" t="s">
         <v>568</v>
       </c>
       <c r="D1268" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="1269" spans="1:4" x14ac:dyDescent="0.2">
@@ -23382,13 +23382,13 @@
         <v>320</v>
       </c>
       <c r="B1269" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1269" t="s">
         <v>462</v>
       </c>
       <c r="D1269" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="1270" spans="1:4" x14ac:dyDescent="0.2">
@@ -23396,13 +23396,13 @@
         <v>320</v>
       </c>
       <c r="B1270" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1270" t="s">
         <v>471</v>
       </c>
       <c r="D1270" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="1271" spans="1:4" x14ac:dyDescent="0.2">
@@ -23410,13 +23410,13 @@
         <v>327</v>
       </c>
       <c r="B1271" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1271" t="s">
         <v>409</v>
       </c>
       <c r="D1271" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="1272" spans="1:4" x14ac:dyDescent="0.2">
@@ -23424,13 +23424,13 @@
         <v>320</v>
       </c>
       <c r="B1272" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1272" t="s">
         <v>353</v>
       </c>
       <c r="D1272" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1273" spans="1:4" x14ac:dyDescent="0.2">
@@ -23438,13 +23438,13 @@
         <v>320</v>
       </c>
       <c r="B1273" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1273" t="s">
         <v>360</v>
       </c>
       <c r="D1273" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="1274" spans="1:4" x14ac:dyDescent="0.2">
@@ -23452,13 +23452,13 @@
         <v>320</v>
       </c>
       <c r="B1274" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1274" t="s">
         <v>471</v>
       </c>
       <c r="D1274" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="1275" spans="1:4" x14ac:dyDescent="0.2">
@@ -23466,13 +23466,13 @@
         <v>327</v>
       </c>
       <c r="B1275" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1275" t="s">
         <v>679</v>
       </c>
       <c r="D1275" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1276" spans="1:4" x14ac:dyDescent="0.2">
@@ -23480,13 +23480,13 @@
         <v>327</v>
       </c>
       <c r="B1276" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1276" t="s">
         <v>363</v>
       </c>
       <c r="D1276" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1277" spans="1:4" x14ac:dyDescent="0.2">
@@ -23494,13 +23494,13 @@
         <v>320</v>
       </c>
       <c r="B1277" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1277" t="s">
         <v>371</v>
       </c>
       <c r="D1277" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="1278" spans="1:4" x14ac:dyDescent="0.2">
@@ -23508,13 +23508,13 @@
         <v>320</v>
       </c>
       <c r="B1278" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1278" t="s">
         <v>372</v>
       </c>
       <c r="D1278" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1279" spans="1:4" x14ac:dyDescent="0.2">
@@ -23522,13 +23522,13 @@
         <v>320</v>
       </c>
       <c r="B1279" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1279" t="s">
         <v>475</v>
       </c>
       <c r="D1279" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="1280" spans="1:4" x14ac:dyDescent="0.2">
@@ -23536,13 +23536,13 @@
         <v>320</v>
       </c>
       <c r="B1280" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1280" t="s">
         <v>372</v>
       </c>
       <c r="D1280" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="1281" spans="1:4" x14ac:dyDescent="0.2">
@@ -23550,13 +23550,13 @@
         <v>320</v>
       </c>
       <c r="B1281" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1281" t="s">
         <v>321</v>
       </c>
       <c r="D1281" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="1282" spans="1:4" x14ac:dyDescent="0.2">
@@ -23564,13 +23564,13 @@
         <v>320</v>
       </c>
       <c r="B1282" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1282" t="s">
         <v>475</v>
       </c>
       <c r="D1282" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="1283" spans="1:4" x14ac:dyDescent="0.2">
@@ -23578,13 +23578,13 @@
         <v>337</v>
       </c>
       <c r="B1283" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1283" t="s">
         <v>532</v>
       </c>
       <c r="D1283" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="1284" spans="1:4" x14ac:dyDescent="0.2">
@@ -23592,13 +23592,13 @@
         <v>320</v>
       </c>
       <c r="B1284" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1284" t="s">
         <v>471</v>
       </c>
       <c r="D1284" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="1285" spans="1:4" x14ac:dyDescent="0.2">
@@ -23606,13 +23606,13 @@
         <v>0</v>
       </c>
       <c r="B1285" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1285" t="s">
         <v>378</v>
       </c>
       <c r="D1285" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="1286" spans="1:4" x14ac:dyDescent="0.2">
@@ -23620,13 +23620,13 @@
         <v>320</v>
       </c>
       <c r="B1286" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1286" t="s">
         <v>360</v>
       </c>
       <c r="D1286" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="1287" spans="1:4" x14ac:dyDescent="0.2">
@@ -23634,13 +23634,13 @@
         <v>337</v>
       </c>
       <c r="B1287" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1287" t="s">
         <v>537</v>
       </c>
       <c r="D1287" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1288" spans="1:4" x14ac:dyDescent="0.2">
@@ -23648,13 +23648,13 @@
         <v>320</v>
       </c>
       <c r="B1288" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1288" t="s">
         <v>360</v>
       </c>
       <c r="D1288" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1289" spans="1:4" x14ac:dyDescent="0.2">
@@ -23662,13 +23662,13 @@
         <v>337</v>
       </c>
       <c r="B1289" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1289" t="s">
         <v>339</v>
       </c>
       <c r="D1289" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1290" spans="1:4" x14ac:dyDescent="0.2">
@@ -23676,13 +23676,13 @@
         <v>327</v>
       </c>
       <c r="B1290" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1290" t="s">
         <v>572</v>
       </c>
       <c r="D1290" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="1291" spans="1:4" x14ac:dyDescent="0.2">
@@ -23690,13 +23690,13 @@
         <v>327</v>
       </c>
       <c r="B1291" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1291" t="s">
         <v>421</v>
       </c>
       <c r="D1291" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="1292" spans="1:4" x14ac:dyDescent="0.2">
@@ -23704,13 +23704,13 @@
         <v>320</v>
       </c>
       <c r="B1292" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1292" t="s">
         <v>462</v>
       </c>
       <c r="D1292" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="1293" spans="1:4" x14ac:dyDescent="0.2">
@@ -23718,13 +23718,13 @@
         <v>327</v>
       </c>
       <c r="B1293" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1293" t="s">
         <v>409</v>
       </c>
       <c r="D1293" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="1294" spans="1:4" x14ac:dyDescent="0.2">
@@ -23732,13 +23732,13 @@
         <v>320</v>
       </c>
       <c r="B1294" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1294" t="s">
         <v>369</v>
       </c>
       <c r="D1294" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="1295" spans="1:4" x14ac:dyDescent="0.2">
@@ -23746,13 +23746,13 @@
         <v>320</v>
       </c>
       <c r="B1295" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1295" t="s">
         <v>371</v>
       </c>
       <c r="D1295" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="1296" spans="1:4" x14ac:dyDescent="0.2">
@@ -23760,13 +23760,13 @@
         <v>323</v>
       </c>
       <c r="B1296" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1296" t="s">
         <v>382</v>
       </c>
       <c r="D1296" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="1297" spans="1:4" x14ac:dyDescent="0.2">
@@ -23774,13 +23774,13 @@
         <v>323</v>
       </c>
       <c r="B1297" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1297" t="s">
         <v>380</v>
       </c>
       <c r="D1297" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="1298" spans="1:4" x14ac:dyDescent="0.2">
@@ -23788,13 +23788,13 @@
         <v>0</v>
       </c>
       <c r="B1298" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1298" t="s">
         <v>373</v>
       </c>
       <c r="D1298" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="1299" spans="1:4" x14ac:dyDescent="0.2">
@@ -23802,13 +23802,13 @@
         <v>1</v>
       </c>
       <c r="B1299" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1299" t="s">
         <v>568</v>
       </c>
       <c r="D1299" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="1300" spans="1:4" x14ac:dyDescent="0.2">
@@ -23816,13 +23816,13 @@
         <v>1</v>
       </c>
       <c r="B1300" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1300" t="s">
         <v>568</v>
       </c>
       <c r="D1300" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="1301" spans="1:4" x14ac:dyDescent="0.2">
@@ -23830,13 +23830,13 @@
         <v>320</v>
       </c>
       <c r="B1301" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1301" t="s">
         <v>360</v>
       </c>
       <c r="D1301" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="1302" spans="1:4" x14ac:dyDescent="0.2">
@@ -23844,13 +23844,13 @@
         <v>320</v>
       </c>
       <c r="B1302" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1302" t="s">
         <v>353</v>
       </c>
       <c r="D1302" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="1303" spans="1:4" x14ac:dyDescent="0.2">
@@ -23858,13 +23858,13 @@
         <v>320</v>
       </c>
       <c r="B1303" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1303" t="s">
         <v>462</v>
       </c>
       <c r="D1303" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="1304" spans="1:4" x14ac:dyDescent="0.2">
@@ -23872,13 +23872,13 @@
         <v>327</v>
       </c>
       <c r="B1304" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1304" t="s">
         <v>328</v>
       </c>
       <c r="D1304" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="1305" spans="1:4" x14ac:dyDescent="0.2">
@@ -23886,13 +23886,13 @@
         <v>327</v>
       </c>
       <c r="B1305" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1305" t="s">
         <v>364</v>
       </c>
       <c r="D1305" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="1306" spans="1:4" x14ac:dyDescent="0.2">
@@ -23900,13 +23900,13 @@
         <v>320</v>
       </c>
       <c r="B1306" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1306" t="s">
         <v>369</v>
       </c>
       <c r="D1306" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="1307" spans="1:4" x14ac:dyDescent="0.2">
@@ -23914,13 +23914,13 @@
         <v>323</v>
       </c>
       <c r="B1307" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1307" t="s">
         <v>382</v>
       </c>
       <c r="D1307" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="1308" spans="1:4" x14ac:dyDescent="0.2">
@@ -23928,13 +23928,13 @@
         <v>1</v>
       </c>
       <c r="B1308" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1308" t="s">
         <v>568</v>
       </c>
       <c r="D1308" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1309" spans="1:4" x14ac:dyDescent="0.2">
@@ -23942,13 +23942,13 @@
         <v>337</v>
       </c>
       <c r="B1309" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1309" t="s">
         <v>537</v>
       </c>
       <c r="D1309" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="1310" spans="1:4" x14ac:dyDescent="0.2">
@@ -23956,13 +23956,13 @@
         <v>320</v>
       </c>
       <c r="B1310" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1310" t="s">
         <v>353</v>
       </c>
       <c r="D1310" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1311" spans="1:4" x14ac:dyDescent="0.2">
@@ -23970,13 +23970,13 @@
         <v>327</v>
       </c>
       <c r="B1311" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1311" t="s">
         <v>365</v>
       </c>
       <c r="D1311" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1312" spans="1:4" x14ac:dyDescent="0.2">
@@ -23984,13 +23984,13 @@
         <v>327</v>
       </c>
       <c r="B1312" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1312" t="s">
         <v>363</v>
       </c>
       <c r="D1312" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="1313" spans="1:4" x14ac:dyDescent="0.2">
@@ -23998,13 +23998,13 @@
         <v>323</v>
       </c>
       <c r="B1313" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1313" t="s">
         <v>380</v>
       </c>
       <c r="D1313" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="1314" spans="1:4" x14ac:dyDescent="0.2">
@@ -24012,13 +24012,13 @@
         <v>323</v>
       </c>
       <c r="B1314" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1314" t="s">
         <v>518</v>
       </c>
       <c r="D1314" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="1315" spans="1:4" x14ac:dyDescent="0.2">
@@ -24026,13 +24026,13 @@
         <v>337</v>
       </c>
       <c r="B1315" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1315" t="s">
         <v>551</v>
       </c>
       <c r="D1315" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="1316" spans="1:4" x14ac:dyDescent="0.2">
@@ -24040,13 +24040,13 @@
         <v>337</v>
       </c>
       <c r="B1316" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1316" t="s">
         <v>537</v>
       </c>
       <c r="D1316" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="1317" spans="1:4" x14ac:dyDescent="0.2">
@@ -24054,13 +24054,13 @@
         <v>320</v>
       </c>
       <c r="B1317" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1317" t="s">
         <v>353</v>
       </c>
       <c r="D1317" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="1318" spans="1:4" x14ac:dyDescent="0.2">
@@ -24068,13 +24068,13 @@
         <v>327</v>
       </c>
       <c r="B1318" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1318" t="s">
         <v>414</v>
       </c>
       <c r="D1318" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="1319" spans="1:4" x14ac:dyDescent="0.2">
@@ -24082,13 +24082,13 @@
         <v>327</v>
       </c>
       <c r="B1319" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1319" t="s">
         <v>679</v>
       </c>
       <c r="D1319" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="1320" spans="1:4" x14ac:dyDescent="0.2">
@@ -24096,13 +24096,13 @@
         <v>0</v>
       </c>
       <c r="B1320" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1320" t="s">
         <v>373</v>
       </c>
       <c r="D1320" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="1321" spans="1:4" x14ac:dyDescent="0.2">
@@ -24110,13 +24110,13 @@
         <v>337</v>
       </c>
       <c r="B1321" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1321" t="s">
         <v>341</v>
       </c>
       <c r="D1321" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="1322" spans="1:4" x14ac:dyDescent="0.2">
@@ -24124,13 +24124,13 @@
         <v>337</v>
       </c>
       <c r="B1322" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1322" t="s">
         <v>537</v>
       </c>
       <c r="D1322" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="1323" spans="1:4" x14ac:dyDescent="0.2">
@@ -24138,13 +24138,13 @@
         <v>327</v>
       </c>
       <c r="B1323" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1323" t="s">
         <v>387</v>
       </c>
       <c r="D1323" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="1324" spans="1:4" x14ac:dyDescent="0.2">
@@ -24152,13 +24152,13 @@
         <v>327</v>
       </c>
       <c r="B1324" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1324" t="s">
         <v>387</v>
       </c>
       <c r="D1324" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="1325" spans="1:4" x14ac:dyDescent="0.2">
@@ -24166,13 +24166,13 @@
         <v>327</v>
       </c>
       <c r="B1325" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1325" t="s">
         <v>426</v>
       </c>
       <c r="D1325" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="1326" spans="1:4" x14ac:dyDescent="0.2">
@@ -24180,13 +24180,13 @@
         <v>0</v>
       </c>
       <c r="B1326" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1326" t="s">
         <v>504</v>
       </c>
       <c r="D1326" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="1327" spans="1:4" x14ac:dyDescent="0.2">
@@ -24194,13 +24194,13 @@
         <v>337</v>
       </c>
       <c r="B1327" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1327" t="s">
         <v>571</v>
       </c>
       <c r="D1327" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1328" spans="1:4" x14ac:dyDescent="0.2">
@@ -24208,13 +24208,13 @@
         <v>327</v>
       </c>
       <c r="B1328" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1328" t="s">
         <v>387</v>
       </c>
       <c r="D1328" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="1329" spans="1:4" x14ac:dyDescent="0.2">
@@ -24222,13 +24222,13 @@
         <v>323</v>
       </c>
       <c r="B1329" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1329" t="s">
         <v>379</v>
       </c>
       <c r="D1329" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="1330" spans="1:4" x14ac:dyDescent="0.2">
@@ -24236,13 +24236,13 @@
         <v>320</v>
       </c>
       <c r="B1330" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1330" t="s">
         <v>371</v>
       </c>
       <c r="D1330" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="1331" spans="1:4" x14ac:dyDescent="0.2">
@@ -24250,13 +24250,13 @@
         <v>337</v>
       </c>
       <c r="B1331" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1331" t="s">
         <v>339</v>
       </c>
       <c r="D1331" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="1332" spans="1:4" x14ac:dyDescent="0.2">
@@ -24264,13 +24264,13 @@
         <v>323</v>
       </c>
       <c r="B1332" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1332" t="s">
         <v>382</v>
       </c>
       <c r="D1332" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="1333" spans="1:4" x14ac:dyDescent="0.2">
@@ -24278,13 +24278,13 @@
         <v>327</v>
       </c>
       <c r="B1333" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1333" t="s">
         <v>364</v>
       </c>
       <c r="D1333" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1334" spans="1:4" x14ac:dyDescent="0.2">
@@ -24292,13 +24292,13 @@
         <v>337</v>
       </c>
       <c r="B1334" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1334" t="s">
         <v>565</v>
       </c>
       <c r="D1334" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1335" spans="1:4" x14ac:dyDescent="0.2">
@@ -24306,13 +24306,13 @@
         <v>327</v>
       </c>
       <c r="B1335" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1335" t="s">
         <v>431</v>
       </c>
       <c r="D1335" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1336" spans="1:4" x14ac:dyDescent="0.2">
@@ -24320,13 +24320,13 @@
         <v>1</v>
       </c>
       <c r="B1336" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1336" t="s">
         <v>361</v>
       </c>
       <c r="D1336" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="1337" spans="1:4" x14ac:dyDescent="0.2">
@@ -24334,13 +24334,13 @@
         <v>337</v>
       </c>
       <c r="B1337" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1337" t="s">
         <v>571</v>
       </c>
       <c r="D1337" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="1338" spans="1:4" x14ac:dyDescent="0.2">
@@ -24348,13 +24348,13 @@
         <v>1</v>
       </c>
       <c r="B1338" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1338" t="s">
         <v>574</v>
       </c>
       <c r="D1338" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="1339" spans="1:4" x14ac:dyDescent="0.2">
@@ -24362,13 +24362,13 @@
         <v>0</v>
       </c>
       <c r="B1339" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1339" t="s">
         <v>346</v>
       </c>
       <c r="D1339" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1340" spans="1:4" x14ac:dyDescent="0.2">
@@ -24376,13 +24376,13 @@
         <v>0</v>
       </c>
       <c r="B1340" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1340" t="s">
         <v>375</v>
       </c>
       <c r="D1340" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="1341" spans="1:4" x14ac:dyDescent="0.2">
@@ -24390,13 +24390,13 @@
         <v>0</v>
       </c>
       <c r="B1341" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1341" t="s">
         <v>376</v>
       </c>
       <c r="D1341" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="1342" spans="1:4" x14ac:dyDescent="0.2">
@@ -24404,13 +24404,13 @@
         <v>320</v>
       </c>
       <c r="B1342" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1342" t="s">
         <v>325</v>
       </c>
       <c r="D1342" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="1343" spans="1:4" x14ac:dyDescent="0.2">
@@ -24418,13 +24418,13 @@
         <v>1</v>
       </c>
       <c r="B1343" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1343" t="s">
         <v>367</v>
       </c>
       <c r="D1343" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="1344" spans="1:4" x14ac:dyDescent="0.2">
@@ -24432,13 +24432,13 @@
         <v>320</v>
       </c>
       <c r="B1344" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1344" t="s">
         <v>475</v>
       </c>
       <c r="D1344" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="1345" spans="1:4" x14ac:dyDescent="0.2">
@@ -24446,13 +24446,13 @@
         <v>337</v>
       </c>
       <c r="B1345" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1345" t="s">
         <v>571</v>
       </c>
       <c r="D1345" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="1346" spans="1:4" x14ac:dyDescent="0.2">
@@ -24460,13 +24460,13 @@
         <v>327</v>
       </c>
       <c r="B1346" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1346" t="s">
         <v>363</v>
       </c>
       <c r="D1346" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="1347" spans="1:4" x14ac:dyDescent="0.2">
@@ -24474,13 +24474,13 @@
         <v>327</v>
       </c>
       <c r="B1347" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1347" t="s">
         <v>366</v>
       </c>
       <c r="D1347" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1348" spans="1:4" x14ac:dyDescent="0.2">
@@ -24488,13 +24488,13 @@
         <v>0</v>
       </c>
       <c r="B1348" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1348" t="s">
         <v>373</v>
       </c>
       <c r="D1348" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="1349" spans="1:4" x14ac:dyDescent="0.2">
@@ -24502,13 +24502,13 @@
         <v>320</v>
       </c>
       <c r="B1349" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1349" t="s">
         <v>462</v>
       </c>
       <c r="D1349" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="1350" spans="1:4" x14ac:dyDescent="0.2">
@@ -24516,13 +24516,13 @@
         <v>327</v>
       </c>
       <c r="B1350" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1350" t="s">
         <v>409</v>
       </c>
       <c r="D1350" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="1351" spans="1:4" x14ac:dyDescent="0.2">
@@ -24530,13 +24530,13 @@
         <v>323</v>
       </c>
       <c r="B1351" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1351" t="s">
         <v>380</v>
       </c>
       <c r="D1351" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="1352" spans="1:4" x14ac:dyDescent="0.2">
@@ -24544,13 +24544,13 @@
         <v>320</v>
       </c>
       <c r="B1352" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1352" t="s">
         <v>462</v>
       </c>
       <c r="D1352" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="1353" spans="1:4" x14ac:dyDescent="0.2">
@@ -24558,13 +24558,13 @@
         <v>320</v>
       </c>
       <c r="B1353" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1353" t="s">
         <v>372</v>
       </c>
       <c r="D1353" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="1354" spans="1:4" x14ac:dyDescent="0.2">
@@ -24572,13 +24572,13 @@
         <v>0</v>
       </c>
       <c r="B1354" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1354" t="s">
         <v>375</v>
       </c>
       <c r="D1354" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="1355" spans="1:4" x14ac:dyDescent="0.2">
@@ -24586,13 +24586,13 @@
         <v>327</v>
       </c>
       <c r="B1355" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1355" t="s">
         <v>573</v>
       </c>
       <c r="D1355" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="1356" spans="1:4" x14ac:dyDescent="0.2">
@@ -24600,13 +24600,13 @@
         <v>327</v>
       </c>
       <c r="B1356" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1356" t="s">
         <v>384</v>
       </c>
       <c r="D1356" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="1357" spans="1:4" x14ac:dyDescent="0.2">
@@ -24614,13 +24614,13 @@
         <v>320</v>
       </c>
       <c r="B1357" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1357" t="s">
         <v>462</v>
       </c>
       <c r="D1357" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="1358" spans="1:4" x14ac:dyDescent="0.2">
@@ -24628,13 +24628,13 @@
         <v>320</v>
       </c>
       <c r="B1358" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1358" t="s">
         <v>360</v>
       </c>
       <c r="D1358" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="1359" spans="1:4" x14ac:dyDescent="0.2">
@@ -24642,13 +24642,13 @@
         <v>337</v>
       </c>
       <c r="B1359" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1359" t="s">
         <v>537</v>
       </c>
       <c r="D1359" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="1360" spans="1:4" x14ac:dyDescent="0.2">
@@ -24656,13 +24656,13 @@
         <v>320</v>
       </c>
       <c r="B1360" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1360" t="s">
         <v>374</v>
       </c>
       <c r="D1360" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="1361" spans="1:4" x14ac:dyDescent="0.2">
@@ -24670,13 +24670,13 @@
         <v>337</v>
       </c>
       <c r="B1361" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1361" t="s">
         <v>339</v>
       </c>
       <c r="D1361" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="1362" spans="1:4" x14ac:dyDescent="0.2">
@@ -24684,13 +24684,13 @@
         <v>327</v>
       </c>
       <c r="B1362" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1362" t="s">
         <v>573</v>
       </c>
       <c r="D1362" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="1363" spans="1:4" x14ac:dyDescent="0.2">
@@ -24698,13 +24698,13 @@
         <v>327</v>
       </c>
       <c r="B1363" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1363" t="s">
         <v>365</v>
       </c>
       <c r="D1363" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1364" spans="1:4" x14ac:dyDescent="0.2">
@@ -24712,13 +24712,13 @@
         <v>327</v>
       </c>
       <c r="B1364" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1364" t="s">
         <v>421</v>
       </c>
       <c r="D1364" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="1365" spans="1:4" x14ac:dyDescent="0.2">
@@ -24726,13 +24726,13 @@
         <v>323</v>
       </c>
       <c r="B1365" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1365" t="s">
         <v>324</v>
       </c>
       <c r="D1365" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="1366" spans="1:4" x14ac:dyDescent="0.2">
@@ -24740,13 +24740,13 @@
         <v>0</v>
       </c>
       <c r="B1366" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1366" t="s">
         <v>373</v>
       </c>
       <c r="D1366" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="1367" spans="1:4" x14ac:dyDescent="0.2">
@@ -24754,13 +24754,13 @@
         <v>1</v>
       </c>
       <c r="B1367" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1367" t="s">
         <v>444</v>
       </c>
       <c r="D1367" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="1368" spans="1:4" x14ac:dyDescent="0.2">
@@ -24768,13 +24768,13 @@
         <v>327</v>
       </c>
       <c r="B1368" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1368" t="s">
         <v>366</v>
       </c>
       <c r="D1368" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="1369" spans="1:4" x14ac:dyDescent="0.2">
@@ -24782,13 +24782,13 @@
         <v>337</v>
       </c>
       <c r="B1369" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1369" t="s">
         <v>540</v>
       </c>
       <c r="D1369" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="1370" spans="1:4" x14ac:dyDescent="0.2">
@@ -24796,13 +24796,13 @@
         <v>337</v>
       </c>
       <c r="B1370" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1370" t="s">
         <v>339</v>
       </c>
       <c r="D1370" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="1371" spans="1:4" x14ac:dyDescent="0.2">
@@ -24810,13 +24810,13 @@
         <v>320</v>
       </c>
       <c r="B1371" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1371" t="s">
         <v>471</v>
       </c>
       <c r="D1371" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="1372" spans="1:4" x14ac:dyDescent="0.2">
@@ -24824,13 +24824,13 @@
         <v>327</v>
       </c>
       <c r="B1372" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1372" t="s">
         <v>328</v>
       </c>
       <c r="D1372" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1373" spans="1:4" x14ac:dyDescent="0.2">
@@ -24838,13 +24838,13 @@
         <v>323</v>
       </c>
       <c r="B1373" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1373" t="s">
         <v>324</v>
       </c>
       <c r="D1373" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="1374" spans="1:4" x14ac:dyDescent="0.2">
@@ -24852,13 +24852,13 @@
         <v>327</v>
       </c>
       <c r="B1374" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1374" t="s">
         <v>573</v>
       </c>
       <c r="D1374" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="1375" spans="1:4" x14ac:dyDescent="0.2">
@@ -24866,13 +24866,13 @@
         <v>327</v>
       </c>
       <c r="B1375" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1375" t="s">
         <v>365</v>
       </c>
       <c r="D1375" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="1376" spans="1:4" x14ac:dyDescent="0.2">
@@ -24880,13 +24880,13 @@
         <v>320</v>
       </c>
       <c r="B1376" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1376" t="s">
         <v>325</v>
       </c>
       <c r="D1376" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="1377" spans="1:4" x14ac:dyDescent="0.2">
@@ -24894,13 +24894,13 @@
         <v>320</v>
       </c>
       <c r="B1377" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1377" t="s">
         <v>325</v>
       </c>
       <c r="D1377" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="1378" spans="1:4" x14ac:dyDescent="0.2">
@@ -24908,13 +24908,13 @@
         <v>327</v>
       </c>
       <c r="B1378" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1378" t="s">
         <v>366</v>
       </c>
       <c r="D1378" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="1379" spans="1:4" x14ac:dyDescent="0.2">
@@ -24922,13 +24922,13 @@
         <v>337</v>
       </c>
       <c r="B1379" s="9" t="s">
-        <v>1352</v>
+        <v>18</v>
       </c>
       <c r="C1379" t="s">
         <v>339</v>
       </c>
       <c r="D1379" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="1380" spans="1:4" x14ac:dyDescent="0.2">
@@ -24936,13 +24936,13 @@
         <v>327</v>
       </c>
       <c r="B1380" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1380" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D1380" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="1381" spans="1:4" x14ac:dyDescent="0.2">
@@ -24950,13 +24950,13 @@
         <v>1</v>
       </c>
       <c r="B1381" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1381" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="D1381" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="1382" spans="1:4" x14ac:dyDescent="0.2">
@@ -24964,13 +24964,13 @@
         <v>337</v>
       </c>
       <c r="B1382" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1382" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D1382" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="1383" spans="1:4" x14ac:dyDescent="0.2">
@@ -24978,13 +24978,13 @@
         <v>0</v>
       </c>
       <c r="B1383" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1383" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D1383" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1384" spans="1:4" x14ac:dyDescent="0.2">
@@ -24992,13 +24992,13 @@
         <v>0</v>
       </c>
       <c r="B1384" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1384" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D1384" t="s">
         <v>1519</v>
-      </c>
-      <c r="D1384" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="1385" spans="1:4" x14ac:dyDescent="0.2">
@@ -25006,13 +25006,13 @@
         <v>323</v>
       </c>
       <c r="B1385" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1385" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="D1385" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="1386" spans="1:4" x14ac:dyDescent="0.2">
@@ -25020,13 +25020,13 @@
         <v>323</v>
       </c>
       <c r="B1386" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1386" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="D1386" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="1387" spans="1:4" x14ac:dyDescent="0.2">
@@ -25034,13 +25034,13 @@
         <v>323</v>
       </c>
       <c r="B1387" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1387" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="D1387" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="1388" spans="1:4" x14ac:dyDescent="0.2">
@@ -25048,13 +25048,13 @@
         <v>320</v>
       </c>
       <c r="B1388" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1388" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="D1388" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="1389" spans="1:4" x14ac:dyDescent="0.2">
@@ -25062,13 +25062,13 @@
         <v>0</v>
       </c>
       <c r="B1389" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1389" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D1389" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="1390" spans="1:4" x14ac:dyDescent="0.2">
@@ -25076,13 +25076,13 @@
         <v>327</v>
       </c>
       <c r="B1390" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1390" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="D1390" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="1391" spans="1:4" x14ac:dyDescent="0.2">
@@ -25090,13 +25090,13 @@
         <v>1</v>
       </c>
       <c r="B1391" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1391" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="D1391" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="1392" spans="1:4" x14ac:dyDescent="0.2">
@@ -25104,13 +25104,13 @@
         <v>1</v>
       </c>
       <c r="B1392" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1392" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="D1392" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="1393" spans="1:4" x14ac:dyDescent="0.2">
@@ -25118,13 +25118,13 @@
         <v>323</v>
       </c>
       <c r="B1393" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1393" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="D1393" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="1394" spans="1:4" x14ac:dyDescent="0.2">
@@ -25132,13 +25132,13 @@
         <v>1</v>
       </c>
       <c r="B1394" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1394" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="D1394" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="1395" spans="1:4" x14ac:dyDescent="0.2">
@@ -25146,13 +25146,13 @@
         <v>323</v>
       </c>
       <c r="B1395" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1395" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="D1395" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="1396" spans="1:4" x14ac:dyDescent="0.2">
@@ -25160,13 +25160,13 @@
         <v>0</v>
       </c>
       <c r="B1396" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1396" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="D1396" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1397" spans="1:4" x14ac:dyDescent="0.2">
@@ -25174,13 +25174,13 @@
         <v>1</v>
       </c>
       <c r="B1397" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1397" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="D1397" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="1398" spans="1:4" x14ac:dyDescent="0.2">
@@ -25188,13 +25188,13 @@
         <v>337</v>
       </c>
       <c r="B1398" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1398" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="D1398" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1399" spans="1:4" x14ac:dyDescent="0.2">
@@ -25202,13 +25202,13 @@
         <v>0</v>
       </c>
       <c r="B1399" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1399" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="D1399" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="1400" spans="1:4" x14ac:dyDescent="0.2">
@@ -25216,13 +25216,13 @@
         <v>1</v>
       </c>
       <c r="B1400" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1400" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D1400" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="1401" spans="1:4" x14ac:dyDescent="0.2">
@@ -25230,13 +25230,13 @@
         <v>1</v>
       </c>
       <c r="B1401" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1401" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="D1401" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1402" spans="1:4" x14ac:dyDescent="0.2">
@@ -25244,13 +25244,13 @@
         <v>0</v>
       </c>
       <c r="B1402" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1402" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="D1402" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1403" spans="1:4" x14ac:dyDescent="0.2">
@@ -25258,13 +25258,13 @@
         <v>0</v>
       </c>
       <c r="B1403" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1403" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="D1403" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="1404" spans="1:4" x14ac:dyDescent="0.2">
@@ -25272,13 +25272,13 @@
         <v>337</v>
       </c>
       <c r="B1404" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1404" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="D1404" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="1405" spans="1:4" x14ac:dyDescent="0.2">
@@ -25286,13 +25286,13 @@
         <v>1</v>
       </c>
       <c r="B1405" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1405" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="D1405" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="1406" spans="1:4" x14ac:dyDescent="0.2">
@@ -25300,13 +25300,13 @@
         <v>0</v>
       </c>
       <c r="B1406" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1406" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D1406" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1407" spans="1:4" x14ac:dyDescent="0.2">
@@ -25314,13 +25314,13 @@
         <v>323</v>
       </c>
       <c r="B1407" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1407" t="s">
         <v>380</v>
       </c>
       <c r="D1407" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="1408" spans="1:4" x14ac:dyDescent="0.2">
@@ -25328,13 +25328,13 @@
         <v>0</v>
       </c>
       <c r="B1408" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1408" t="s">
         <v>373</v>
       </c>
       <c r="D1408" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="1409" spans="1:4" x14ac:dyDescent="0.2">
@@ -25342,13 +25342,13 @@
         <v>323</v>
       </c>
       <c r="B1409" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1409" t="s">
         <v>382</v>
       </c>
       <c r="D1409" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="1410" spans="1:4" x14ac:dyDescent="0.2">
@@ -25356,13 +25356,13 @@
         <v>337</v>
       </c>
       <c r="B1410" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1410" t="s">
         <v>540</v>
       </c>
       <c r="D1410" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="1411" spans="1:4" x14ac:dyDescent="0.2">
@@ -25370,13 +25370,13 @@
         <v>320</v>
       </c>
       <c r="B1411" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1411" t="s">
         <v>462</v>
       </c>
       <c r="D1411" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1412" spans="1:4" x14ac:dyDescent="0.2">
@@ -25390,7 +25390,7 @@
         <v>372</v>
       </c>
       <c r="D1412" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1413" spans="1:4" ht="15" x14ac:dyDescent="0.2">
@@ -25398,12 +25398,26 @@
         <v>320</v>
       </c>
       <c r="B1413" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C1413" t="s">
         <v>372</v>
       </c>
       <c r="D1413" s="18" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1414" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1414" s="9" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>409</v>
+      </c>
+      <c r="D1414" t="s">
         <v>1564</v>
       </c>
     </row>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BB8D8A-0168-4D11-BC9C-8016EF0F51E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE50895-8585-44A4-86A5-84739731B117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1378</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1414</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5656" uniqueCount="1565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5660" uniqueCount="1566">
   <si>
     <t>VINH</t>
   </si>
@@ -4723,6 +4723,9 @@
   </si>
   <si>
     <t>BHX CU XA DO THANH</t>
+  </si>
+  <si>
+    <t>BS Mart duong so 10</t>
   </si>
 </sst>
 </file>
@@ -5616,7 +5619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1414"/>
+  <dimension ref="A1:D1415"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -25407,7 +25410,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="1414" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1414" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1414" t="s">
         <v>327</v>
       </c>
@@ -25421,8 +25424,22 @@
         <v>1564</v>
       </c>
     </row>
+    <row r="1415" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1415" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1415" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>330</v>
+      </c>
+      <c r="D1415" s="3" t="s">
+        <v>1565</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D1378" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:D1414" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D1209">
       <sortCondition ref="C1:C1209"/>
     </sortState>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE50895-8585-44A4-86A5-84739731B117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7DF75B-B422-43D9-8F47-594554465DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5660" uniqueCount="1566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5664" uniqueCount="1568">
   <si>
     <t>VINH</t>
   </si>
@@ -4726,6 +4726,12 @@
   </si>
   <si>
     <t>BS Mart duong so 10</t>
+  </si>
+  <si>
+    <t>SH</t>
+  </si>
+  <si>
+    <t>San Ha Binh Hung 2</t>
   </si>
 </sst>
 </file>
@@ -5619,7 +5625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1415"/>
+  <dimension ref="A1:D1416"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -25436,6 +25442,20 @@
       </c>
       <c r="D1415" s="3" t="s">
         <v>1565</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1416" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1416" s="9" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>330</v>
+      </c>
+      <c r="D1416" s="3" t="s">
+        <v>1567</v>
       </c>
     </row>
   </sheetData>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CDBECO\Desktop\data on ưeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF51BE9-FE42-4C6B-9772-6ED99709FB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24600ADE-B2BC-4824-88F9-6910CAE08383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5644" uniqueCount="1562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5652" uniqueCount="1564">
   <si>
     <t>VINH</t>
   </si>
@@ -4714,6 +4714,12 @@
   </si>
   <si>
     <t>Phuong Binh Thuan</t>
+  </si>
+  <si>
+    <t>02203-CO.OPFOOD MIZUKI</t>
+  </si>
+  <si>
+    <t>GS25 MIZUKI</t>
   </si>
 </sst>
 </file>
@@ -4723,7 +4729,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4746,17 +4752,28 @@
       <family val="3"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="GMV Linotte"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="GMV Linotte"/>
+      <family val="3"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="GMV Linotte"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -4825,9 +4842,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4856,23 +4873,30 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5607,7 +5631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1411"/>
+  <dimension ref="A1:D1413"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -9574,7 +9598,7 @@
       <c r="C283" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="D283" s="15" t="s">
+      <c r="D283" s="13" t="s">
         <v>1372</v>
       </c>
     </row>
@@ -22479,10 +22503,10 @@
       <c r="B1205" s="8" t="s">
         <v>1334</v>
       </c>
-      <c r="C1205" t="s">
+      <c r="C1205" s="14" t="s">
         <v>499</v>
       </c>
-      <c r="D1205" t="s">
+      <c r="D1205" s="14" t="s">
         <v>1328</v>
       </c>
     </row>
@@ -22493,10 +22517,10 @@
       <c r="B1206" s="8" t="s">
         <v>1334</v>
       </c>
-      <c r="C1206" t="s">
+      <c r="C1206" s="14" t="s">
         <v>540</v>
       </c>
-      <c r="D1206" t="s">
+      <c r="D1206" s="14" t="s">
         <v>1329</v>
       </c>
     </row>
@@ -22507,10 +22531,10 @@
       <c r="B1207" s="8" t="s">
         <v>1334</v>
       </c>
-      <c r="C1207" t="s">
+      <c r="C1207" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="D1207" t="s">
+      <c r="D1207" s="14" t="s">
         <v>1330</v>
       </c>
     </row>
@@ -22521,10 +22545,10 @@
       <c r="B1208" s="8" t="s">
         <v>1334</v>
       </c>
-      <c r="C1208" t="s">
+      <c r="C1208" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="D1208" t="s">
+      <c r="D1208" s="14" t="s">
         <v>1331</v>
       </c>
     </row>
@@ -22535,10 +22559,10 @@
       <c r="B1209" s="8" t="s">
         <v>1334</v>
       </c>
-      <c r="C1209" t="s">
+      <c r="C1209" s="14" t="s">
         <v>1333</v>
       </c>
-      <c r="D1209" t="s">
+      <c r="D1209" s="14" t="s">
         <v>1332</v>
       </c>
     </row>
@@ -22549,10 +22573,10 @@
       <c r="B1210" s="11" t="s">
         <v>1309</v>
       </c>
-      <c r="C1210" s="12" t="s">
+      <c r="C1210" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="D1210" s="12" t="s">
+      <c r="D1210" s="15" t="s">
         <v>1335</v>
       </c>
     </row>
@@ -22563,10 +22587,10 @@
       <c r="B1211" s="11" t="s">
         <v>1309</v>
       </c>
-      <c r="C1211" s="12" t="s">
+      <c r="C1211" s="15" t="s">
         <v>348</v>
       </c>
-      <c r="D1211" s="12" t="s">
+      <c r="D1211" s="15" t="s">
         <v>1336</v>
       </c>
     </row>
@@ -22574,13 +22598,13 @@
       <c r="A1212" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1212" s="9" t="s">
+      <c r="B1212" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1212" t="s">
+      <c r="C1212" s="14" t="s">
         <v>569</v>
       </c>
-      <c r="D1212" t="s">
+      <c r="D1212" s="14" t="s">
         <v>1337</v>
       </c>
     </row>
@@ -22588,13 +22612,13 @@
       <c r="A1213" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1213" s="9" t="s">
+      <c r="B1213" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="C1213" t="s">
+      <c r="C1213" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="D1213" t="s">
+      <c r="D1213" s="14" t="s">
         <v>1338</v>
       </c>
     </row>
@@ -22602,13 +22626,13 @@
       <c r="A1214" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1214" s="9" t="s">
+      <c r="B1214" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="C1214" t="s">
+      <c r="C1214" s="14" t="s">
         <v>569</v>
       </c>
-      <c r="D1214" t="s">
+      <c r="D1214" s="14" t="s">
         <v>1339</v>
       </c>
     </row>
@@ -22616,13 +22640,13 @@
       <c r="A1215" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1215" s="13" t="s">
+      <c r="B1215" s="17" t="s">
         <v>122</v>
       </c>
       <c r="C1215" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="D1215" s="14" t="s">
+      <c r="D1215" s="18" t="s">
         <v>1342</v>
       </c>
     </row>
@@ -22630,13 +22654,13 @@
       <c r="A1216" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1216" s="9" t="s">
+      <c r="B1216" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1216" t="s">
+      <c r="C1216" s="14" t="s">
         <v>544</v>
       </c>
-      <c r="D1216" t="s">
+      <c r="D1216" s="14" t="s">
         <v>1340</v>
       </c>
     </row>
@@ -22644,13 +22668,13 @@
       <c r="A1217" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1217" s="9" t="s">
+      <c r="B1217" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1217" t="s">
+      <c r="C1217" s="14" t="s">
         <v>540</v>
       </c>
-      <c r="D1217" t="s">
+      <c r="D1217" s="14" t="s">
         <v>1341</v>
       </c>
     </row>
@@ -22658,13 +22682,13 @@
       <c r="A1218" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1218" s="9" t="s">
+      <c r="B1218" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C1218" t="s">
+      <c r="C1218" s="14" t="s">
         <v>527</v>
       </c>
-      <c r="D1218" t="s">
+      <c r="D1218" s="14" t="s">
         <v>1344</v>
       </c>
     </row>
@@ -22672,13 +22696,13 @@
       <c r="A1219" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1219" s="9" t="s">
+      <c r="B1219" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C1219" t="s">
+      <c r="C1219" s="14" t="s">
         <v>527</v>
       </c>
-      <c r="D1219" t="s">
+      <c r="D1219" s="14" t="s">
         <v>1345</v>
       </c>
     </row>
@@ -22686,13 +22710,13 @@
       <c r="A1220" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1220" s="9" t="s">
+      <c r="B1220" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1220" t="s">
+      <c r="C1220" s="14" t="s">
         <v>555</v>
       </c>
-      <c r="D1220" t="s">
+      <c r="D1220" s="14" t="s">
         <v>1346</v>
       </c>
     </row>
@@ -22700,13 +22724,13 @@
       <c r="A1221" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1221" s="9" t="s">
+      <c r="B1221" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1221" t="s">
+      <c r="C1221" s="14" t="s">
         <v>562</v>
       </c>
-      <c r="D1221" t="s">
+      <c r="D1221" s="14" t="s">
         <v>1347</v>
       </c>
     </row>
@@ -22714,13 +22738,13 @@
       <c r="A1222" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1222" s="9" t="s">
+      <c r="B1222" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1222" t="s">
+      <c r="C1222" s="14" t="s">
         <v>493</v>
       </c>
-      <c r="D1222" t="s">
+      <c r="D1222" s="14" t="s">
         <v>1348</v>
       </c>
     </row>
@@ -22728,13 +22752,13 @@
       <c r="A1223" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B1223" s="9" t="s">
+      <c r="B1223" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1223" t="s">
+      <c r="C1223" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="D1223" t="s">
+      <c r="D1223" s="14" t="s">
         <v>1349</v>
       </c>
     </row>
@@ -22742,13 +22766,13 @@
       <c r="A1224" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1224" s="9" t="s">
+      <c r="B1224" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1224" t="s">
+      <c r="C1224" s="14" t="s">
         <v>527</v>
       </c>
-      <c r="D1224" t="s">
+      <c r="D1224" s="14" t="s">
         <v>1350</v>
       </c>
     </row>
@@ -22756,13 +22780,13 @@
       <c r="A1225" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1225" s="9" t="s">
+      <c r="B1225" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1225" t="s">
+      <c r="C1225" s="14" t="s">
         <v>562</v>
       </c>
-      <c r="D1225" s="14" t="s">
+      <c r="D1225" s="18" t="s">
         <v>1351</v>
       </c>
     </row>
@@ -22770,13 +22794,13 @@
       <c r="A1226" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1226" s="9" t="s">
+      <c r="B1226" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1226" t="s">
+      <c r="C1226" s="14" t="s">
         <v>499</v>
       </c>
-      <c r="D1226" t="s">
+      <c r="D1226" s="14" t="s">
         <v>1352</v>
       </c>
     </row>
@@ -22784,13 +22808,13 @@
       <c r="A1227" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1227" s="9" t="s">
+      <c r="B1227" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1227" t="s">
+      <c r="C1227" s="14" t="s">
         <v>558</v>
       </c>
-      <c r="D1227" s="14" t="s">
+      <c r="D1227" s="18" t="s">
         <v>1353</v>
       </c>
     </row>
@@ -22798,13 +22822,13 @@
       <c r="A1228" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1228" s="9" t="s">
+      <c r="B1228" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1228" t="s">
+      <c r="C1228" s="14" t="s">
         <v>499</v>
       </c>
-      <c r="D1228" s="14" t="s">
+      <c r="D1228" s="18" t="s">
         <v>1354</v>
       </c>
     </row>
@@ -22812,13 +22836,13 @@
       <c r="A1229" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1229" s="9" t="s">
+      <c r="B1229" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1229" t="s">
+      <c r="C1229" s="14" t="s">
         <v>558</v>
       </c>
-      <c r="D1229" s="14" t="s">
+      <c r="D1229" s="18" t="s">
         <v>1355</v>
       </c>
     </row>
@@ -22826,13 +22850,13 @@
       <c r="A1230" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1230" s="9" t="s">
+      <c r="B1230" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1230" t="s">
+      <c r="C1230" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="D1230" s="15" t="s">
+      <c r="D1230" s="12" t="s">
         <v>1356</v>
       </c>
     </row>
@@ -22840,13 +22864,13 @@
       <c r="A1231" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B1231" s="9" t="s">
+      <c r="B1231" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1231" t="s">
+      <c r="C1231" s="14" t="s">
         <v>470</v>
       </c>
-      <c r="D1231" s="15" t="s">
+      <c r="D1231" s="12" t="s">
         <v>1357</v>
       </c>
     </row>
@@ -22854,13 +22878,13 @@
       <c r="A1232" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B1232" s="9" t="s">
+      <c r="B1232" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1232" t="s">
+      <c r="C1232" s="14" t="s">
         <v>520</v>
       </c>
-      <c r="D1232" s="15" t="s">
+      <c r="D1232" s="12" t="s">
         <v>1358</v>
       </c>
     </row>
@@ -22868,13 +22892,13 @@
       <c r="A1233" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B1233" s="9" t="s">
+      <c r="B1233" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1233" t="s">
+      <c r="C1233" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D1233" s="16" t="s">
+      <c r="D1233" s="19" t="s">
         <v>1359</v>
       </c>
     </row>
@@ -22882,13 +22906,13 @@
       <c r="A1234" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1234" s="9" t="s">
+      <c r="B1234" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1234" t="s">
+      <c r="C1234" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="D1234" s="16" t="s">
+      <c r="D1234" s="19" t="s">
         <v>1360</v>
       </c>
     </row>
@@ -22896,13 +22920,13 @@
       <c r="A1235" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B1235" s="9" t="s">
+      <c r="B1235" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1235" t="s">
+      <c r="C1235" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="D1235" s="16" t="s">
+      <c r="D1235" s="19" t="s">
         <v>1361</v>
       </c>
     </row>
@@ -22910,13 +22934,13 @@
       <c r="A1236" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B1236" s="9" t="s">
+      <c r="B1236" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1236" t="s">
+      <c r="C1236" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="D1236" s="16" t="s">
+      <c r="D1236" s="19" t="s">
         <v>1362</v>
       </c>
     </row>
@@ -22924,13 +22948,13 @@
       <c r="A1237" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B1237" s="9" t="s">
+      <c r="B1237" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1237" t="s">
+      <c r="C1237" s="14" t="s">
         <v>512</v>
       </c>
-      <c r="D1237" s="16" t="s">
+      <c r="D1237" s="19" t="s">
         <v>1363</v>
       </c>
     </row>
@@ -22938,13 +22962,13 @@
       <c r="A1238" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1238" s="9" t="s">
+      <c r="B1238" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1238" t="s">
+      <c r="C1238" s="14" t="s">
         <v>1365</v>
       </c>
-      <c r="D1238" s="17" t="s">
+      <c r="D1238" s="20" t="s">
         <v>1364</v>
       </c>
     </row>
@@ -22952,13 +22976,13 @@
       <c r="A1239" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B1239" s="9" t="s">
+      <c r="B1239" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1239" t="s">
+      <c r="C1239" s="14" t="s">
         <v>520</v>
       </c>
-      <c r="D1239" s="17" t="s">
+      <c r="D1239" s="20" t="s">
         <v>1366</v>
       </c>
     </row>
@@ -22966,13 +22990,13 @@
       <c r="A1240" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B1240" s="9" t="s">
+      <c r="B1240" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1240" t="s">
+      <c r="C1240" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="D1240" s="17" t="s">
+      <c r="D1240" s="20" t="s">
         <v>1367</v>
       </c>
     </row>
@@ -22980,13 +23004,13 @@
       <c r="A1241" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B1241" s="9" t="s">
+      <c r="B1241" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1241" t="s">
+      <c r="C1241" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="D1241" s="15" t="s">
+      <c r="D1241" s="12" t="s">
         <v>1368</v>
       </c>
     </row>
@@ -22994,13 +23018,13 @@
       <c r="A1242" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1242" s="9" t="s">
+      <c r="B1242" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1242" t="s">
+      <c r="C1242" s="14" t="s">
         <v>566</v>
       </c>
-      <c r="D1242" s="17" t="s">
+      <c r="D1242" s="20" t="s">
         <v>1369</v>
       </c>
     </row>
@@ -23008,13 +23032,13 @@
       <c r="A1243" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1243" s="9" t="s">
+      <c r="B1243" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1243" t="s">
+      <c r="C1243" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="D1243" s="17" t="s">
+      <c r="D1243" s="20" t="s">
         <v>1370</v>
       </c>
     </row>
@@ -23022,13 +23046,13 @@
       <c r="A1244" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="B1244" s="9" t="s">
+      <c r="B1244" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1244" t="s">
+      <c r="C1244" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="D1244" s="17" t="s">
+      <c r="D1244" s="20" t="s">
         <v>1371</v>
       </c>
     </row>
@@ -23036,13 +23060,13 @@
       <c r="A1245" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1245" s="9" t="s">
+      <c r="B1245" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1245" t="s">
+      <c r="C1245" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="D1245" s="15" t="s">
+      <c r="D1245" s="12" t="s">
         <v>1373</v>
       </c>
     </row>
@@ -23067,7 +23091,7 @@
       <c r="B1247" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C1247" t="s">
+      <c r="C1247" s="14" t="s">
         <v>319</v>
       </c>
       <c r="D1247" s="1" t="s">
@@ -23078,2278 +23102,2278 @@
       <c r="A1248" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1248" s="9" t="s">
+      <c r="B1248" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C1248" t="s">
+      <c r="C1248" s="14" t="s">
         <v>1365</v>
       </c>
-      <c r="D1248" t="s">
+      <c r="D1248" s="14" t="s">
         <v>1376</v>
       </c>
     </row>
-    <row r="1249" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1249" t="s">
+    <row r="1249" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1249" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1249" s="9" t="s">
+      <c r="B1249" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1249" t="s">
+      <c r="C1249" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="D1249" t="s">
+      <c r="D1249" s="14" t="s">
         <v>1400</v>
       </c>
     </row>
-    <row r="1250" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1250" t="s">
+    <row r="1250" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1250" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1250" s="9" t="s">
+      <c r="B1250" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1250" t="s">
+      <c r="C1250" s="14" t="s">
         <v>568</v>
       </c>
-      <c r="D1250" t="s">
+      <c r="D1250" s="14" t="s">
         <v>1401</v>
       </c>
     </row>
-    <row r="1251" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1251" t="s">
+    <row r="1251" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1251" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1251" s="9" t="s">
+      <c r="B1251" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1251" t="s">
+      <c r="C1251" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="D1251" t="s">
+      <c r="D1251" s="14" t="s">
         <v>1402</v>
       </c>
     </row>
-    <row r="1252" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1252" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1252" s="9" t="s">
+    <row r="1252" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1252" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1252" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1252" t="s">
+      <c r="C1252" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="D1252" t="s">
+      <c r="D1252" s="14" t="s">
         <v>1403</v>
       </c>
     </row>
-    <row r="1253" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1253" t="s">
+    <row r="1253" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1253" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1253" s="9" t="s">
+      <c r="B1253" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1253" t="s">
+      <c r="C1253" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="D1253" t="s">
+      <c r="D1253" s="14" t="s">
         <v>1404</v>
       </c>
     </row>
-    <row r="1254" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1254" t="s">
+    <row r="1254" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1254" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1254" s="9" t="s">
+      <c r="B1254" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1254" t="s">
+      <c r="C1254" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="D1254" t="s">
+      <c r="D1254" s="14" t="s">
         <v>1405</v>
       </c>
     </row>
-    <row r="1255" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1255" t="s">
+    <row r="1255" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1255" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1255" s="9" t="s">
+      <c r="B1255" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1255" t="s">
+      <c r="C1255" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="D1255" t="s">
+      <c r="D1255" s="14" t="s">
         <v>1406</v>
       </c>
     </row>
-    <row r="1256" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1256" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1256" s="9" t="s">
+    <row r="1256" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1256" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1256" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1256" t="s">
+      <c r="C1256" s="14" t="s">
         <v>555</v>
       </c>
-      <c r="D1256" t="s">
+      <c r="D1256" s="14" t="s">
         <v>1407</v>
       </c>
     </row>
-    <row r="1257" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1257" t="s">
+    <row r="1257" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1257" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1257" s="9" t="s">
+      <c r="B1257" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1257" t="s">
+      <c r="C1257" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="D1257" t="s">
+      <c r="D1257" s="14" t="s">
         <v>1408</v>
       </c>
     </row>
-    <row r="1258" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1258" t="s">
+    <row r="1258" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1258" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1258" s="9" t="s">
+      <c r="B1258" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1258" t="s">
+      <c r="C1258" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="D1258" t="s">
+      <c r="D1258" s="14" t="s">
         <v>1409</v>
       </c>
     </row>
-    <row r="1259" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1259" t="s">
+    <row r="1259" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1259" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1259" s="9" t="s">
+      <c r="B1259" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1259" t="s">
+      <c r="C1259" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="D1259" t="s">
+      <c r="D1259" s="14" t="s">
         <v>1410</v>
       </c>
     </row>
-    <row r="1260" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1260" t="s">
+    <row r="1260" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1260" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1260" s="9" t="s">
+      <c r="B1260" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1260" t="s">
+      <c r="C1260" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="D1260" t="s">
+      <c r="D1260" s="14" t="s">
         <v>1411</v>
       </c>
     </row>
-    <row r="1261" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1261" t="s">
+    <row r="1261" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1261" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1261" s="9" t="s">
+      <c r="B1261" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1261" t="s">
+      <c r="C1261" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="D1261" t="s">
+      <c r="D1261" s="14" t="s">
         <v>1412</v>
       </c>
     </row>
-    <row r="1262" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1262" t="s">
+    <row r="1262" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1262" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1262" s="9" t="s">
+      <c r="B1262" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1262" t="s">
+      <c r="C1262" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="D1262" t="s">
+      <c r="D1262" s="14" t="s">
         <v>1413</v>
       </c>
     </row>
-    <row r="1263" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1263" t="s">
+    <row r="1263" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1263" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1263" s="9" t="s">
+      <c r="B1263" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1263" t="s">
+      <c r="C1263" s="14" t="s">
         <v>563</v>
       </c>
-      <c r="D1263" t="s">
+      <c r="D1263" s="14" t="s">
         <v>1414</v>
       </c>
     </row>
-    <row r="1264" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1264" t="s">
+    <row r="1264" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1264" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1264" s="9" t="s">
+      <c r="B1264" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1264" t="s">
+      <c r="C1264" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="D1264" t="s">
+      <c r="D1264" s="14" t="s">
         <v>1415</v>
       </c>
     </row>
-    <row r="1265" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1265" t="s">
+    <row r="1265" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1265" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1265" s="9" t="s">
+      <c r="B1265" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1265" t="s">
+      <c r="C1265" s="14" t="s">
         <v>466</v>
       </c>
-      <c r="D1265" t="s">
+      <c r="D1265" s="14" t="s">
         <v>1416</v>
       </c>
     </row>
-    <row r="1266" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1266" t="s">
+    <row r="1266" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1266" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1266" s="9" t="s">
+      <c r="B1266" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1266" t="s">
+      <c r="C1266" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="D1266" t="s">
+      <c r="D1266" s="14" t="s">
         <v>1417</v>
       </c>
     </row>
-    <row r="1267" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1267" t="s">
+    <row r="1267" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1267" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1267" s="9" t="s">
+      <c r="B1267" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1267" t="s">
+      <c r="C1267" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="D1267" t="s">
+      <c r="D1267" s="14" t="s">
         <v>1418</v>
       </c>
     </row>
-    <row r="1268" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1268" t="s">
+    <row r="1268" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1268" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1268" s="9" t="s">
+      <c r="B1268" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1268" t="s">
+      <c r="C1268" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="D1268" t="s">
+      <c r="D1268" s="14" t="s">
         <v>1419</v>
       </c>
     </row>
-    <row r="1269" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1269" t="s">
+    <row r="1269" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1269" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1269" s="9" t="s">
+      <c r="B1269" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1269" t="s">
+      <c r="C1269" s="14" t="s">
         <v>466</v>
       </c>
-      <c r="D1269" t="s">
+      <c r="D1269" s="14" t="s">
         <v>1420</v>
       </c>
     </row>
-    <row r="1270" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1270" t="s">
+    <row r="1270" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1270" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1270" s="9" t="s">
+      <c r="B1270" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1270" t="s">
+      <c r="C1270" s="14" t="s">
         <v>674</v>
       </c>
-      <c r="D1270" t="s">
+      <c r="D1270" s="14" t="s">
         <v>1421</v>
       </c>
     </row>
-    <row r="1271" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1271" t="s">
+    <row r="1271" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1271" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1271" s="9" t="s">
+      <c r="B1271" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1271" t="s">
+      <c r="C1271" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="D1271" t="s">
+      <c r="D1271" s="14" t="s">
         <v>1422</v>
       </c>
     </row>
-    <row r="1272" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1272" t="s">
+    <row r="1272" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1272" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1272" s="9" t="s">
+      <c r="B1272" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1272" t="s">
+      <c r="C1272" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="D1272" t="s">
+      <c r="D1272" s="14" t="s">
         <v>1423</v>
       </c>
     </row>
-    <row r="1273" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1273" t="s">
+    <row r="1273" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1273" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1273" s="9" t="s">
+      <c r="B1273" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1273" t="s">
+      <c r="C1273" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="D1273" t="s">
+      <c r="D1273" s="14" t="s">
         <v>1424</v>
       </c>
     </row>
-    <row r="1274" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1274" t="s">
+    <row r="1274" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1274" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1274" s="9" t="s">
+      <c r="B1274" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1274" t="s">
+      <c r="C1274" s="14" t="s">
         <v>470</v>
       </c>
-      <c r="D1274" t="s">
+      <c r="D1274" s="14" t="s">
         <v>1425</v>
       </c>
     </row>
-    <row r="1275" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1275" t="s">
+    <row r="1275" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1275" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1275" s="9" t="s">
+      <c r="B1275" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1275" t="s">
+      <c r="C1275" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="D1275" t="s">
+      <c r="D1275" s="14" t="s">
         <v>1426</v>
       </c>
     </row>
-    <row r="1276" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1276" t="s">
+    <row r="1276" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1276" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1276" s="9" t="s">
+      <c r="B1276" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1276" t="s">
+      <c r="C1276" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="D1276" t="s">
+      <c r="D1276" s="14" t="s">
         <v>1427</v>
       </c>
     </row>
-    <row r="1277" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1277" t="s">
+    <row r="1277" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1277" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1277" s="9" t="s">
+      <c r="B1277" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1277" t="s">
+      <c r="C1277" s="14" t="s">
         <v>470</v>
       </c>
-      <c r="D1277" t="s">
+      <c r="D1277" s="14" t="s">
         <v>1428</v>
       </c>
     </row>
-    <row r="1278" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1278" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1278" s="9" t="s">
+    <row r="1278" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1278" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1278" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1278" t="s">
+      <c r="C1278" s="14" t="s">
         <v>527</v>
       </c>
-      <c r="D1278" t="s">
+      <c r="D1278" s="14" t="s">
         <v>1429</v>
       </c>
     </row>
-    <row r="1279" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1279" t="s">
+    <row r="1279" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1279" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1279" s="9" t="s">
+      <c r="B1279" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1279" t="s">
+      <c r="C1279" s="14" t="s">
         <v>466</v>
       </c>
-      <c r="D1279" t="s">
+      <c r="D1279" s="14" t="s">
         <v>1430</v>
       </c>
     </row>
-    <row r="1280" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1280" t="s">
+    <row r="1280" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1280" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1280" s="9" t="s">
+      <c r="B1280" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1280" t="s">
+      <c r="C1280" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="D1280" t="s">
+      <c r="D1280" s="14" t="s">
         <v>1431</v>
       </c>
     </row>
-    <row r="1281" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1281" t="s">
+    <row r="1281" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1281" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1281" s="9" t="s">
+      <c r="B1281" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1281" t="s">
+      <c r="C1281" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="D1281" t="s">
+      <c r="D1281" s="14" t="s">
         <v>1432</v>
       </c>
     </row>
-    <row r="1282" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1282" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1282" s="9" t="s">
+    <row r="1282" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1282" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1282" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1282" t="s">
+      <c r="C1282" s="14" t="s">
         <v>532</v>
       </c>
-      <c r="D1282" t="s">
+      <c r="D1282" s="14" t="s">
         <v>1433</v>
       </c>
     </row>
-    <row r="1283" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1283" t="s">
+    <row r="1283" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1283" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1283" s="9" t="s">
+      <c r="B1283" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1283" t="s">
+      <c r="C1283" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="D1283" t="s">
+      <c r="D1283" s="14" t="s">
         <v>1434</v>
       </c>
     </row>
-    <row r="1284" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1284" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1284" s="9" t="s">
+    <row r="1284" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1284" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1284" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1284" t="s">
+      <c r="C1284" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="D1284" t="s">
+      <c r="D1284" s="14" t="s">
         <v>1435</v>
       </c>
     </row>
-    <row r="1285" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1285" t="s">
+    <row r="1285" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1285" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1285" s="9" t="s">
+      <c r="B1285" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1285" t="s">
+      <c r="C1285" s="14" t="s">
         <v>567</v>
       </c>
-      <c r="D1285" t="s">
+      <c r="D1285" s="14" t="s">
         <v>1436</v>
       </c>
     </row>
-    <row r="1286" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1286" t="s">
+    <row r="1286" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1286" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1286" s="9" t="s">
+      <c r="B1286" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1286" t="s">
+      <c r="C1286" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="D1286" t="s">
+      <c r="D1286" s="14" t="s">
         <v>1437</v>
       </c>
     </row>
-    <row r="1287" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1287" t="s">
+    <row r="1287" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1287" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1287" s="9" t="s">
+      <c r="B1287" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1287" t="s">
+      <c r="C1287" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="D1287" t="s">
+      <c r="D1287" s="14" t="s">
         <v>1438</v>
       </c>
     </row>
-    <row r="1288" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1288" t="s">
+    <row r="1288" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1288" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1288" s="9" t="s">
+      <c r="B1288" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1288" t="s">
+      <c r="C1288" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="D1288" t="s">
+      <c r="D1288" s="14" t="s">
         <v>1439</v>
       </c>
     </row>
-    <row r="1289" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1289" t="s">
+    <row r="1289" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1289" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1289" s="9" t="s">
+      <c r="B1289" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1289" t="s">
+      <c r="C1289" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="D1289" t="s">
+      <c r="D1289" s="14" t="s">
         <v>1440</v>
       </c>
     </row>
-    <row r="1290" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1290" t="s">
+    <row r="1290" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1290" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1290" s="9" t="s">
+      <c r="B1290" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1290" t="s">
+      <c r="C1290" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="D1290" t="s">
+      <c r="D1290" s="14" t="s">
         <v>1441</v>
       </c>
     </row>
-    <row r="1291" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1291" t="s">
+    <row r="1291" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1291" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1291" s="9" t="s">
+      <c r="B1291" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1291" t="s">
+      <c r="C1291" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="D1291" t="s">
+      <c r="D1291" s="14" t="s">
         <v>1442</v>
       </c>
     </row>
-    <row r="1292" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1292" t="s">
+    <row r="1292" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1292" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1292" s="9" t="s">
+      <c r="B1292" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1292" t="s">
+      <c r="C1292" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D1292" t="s">
+      <c r="D1292" s="14" t="s">
         <v>1443</v>
       </c>
     </row>
-    <row r="1293" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1293" t="s">
+    <row r="1293" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1293" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1293" s="9" t="s">
+      <c r="B1293" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1293" t="s">
+      <c r="C1293" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="D1293" t="s">
+      <c r="D1293" s="14" t="s">
         <v>1444</v>
       </c>
     </row>
-    <row r="1294" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1294" t="s">
+    <row r="1294" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1294" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1294" s="9" t="s">
+      <c r="B1294" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1294" t="s">
+      <c r="C1294" s="14" t="s">
         <v>563</v>
       </c>
-      <c r="D1294" t="s">
+      <c r="D1294" s="14" t="s">
         <v>1445</v>
       </c>
     </row>
-    <row r="1295" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1295" t="s">
+    <row r="1295" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1295" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1295" s="9" t="s">
+      <c r="B1295" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1295" t="s">
+      <c r="C1295" s="14" t="s">
         <v>563</v>
       </c>
-      <c r="D1295" t="s">
+      <c r="D1295" s="14" t="s">
         <v>1446</v>
       </c>
     </row>
-    <row r="1296" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1296" t="s">
+    <row r="1296" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1296" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1296" s="9" t="s">
+      <c r="B1296" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1296" t="s">
+      <c r="C1296" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="D1296" t="s">
+      <c r="D1296" s="14" t="s">
         <v>1447</v>
       </c>
     </row>
-    <row r="1297" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1297" t="s">
+    <row r="1297" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1297" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1297" s="9" t="s">
+      <c r="B1297" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1297" t="s">
+      <c r="C1297" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="D1297" t="s">
+      <c r="D1297" s="14" t="s">
         <v>1448</v>
       </c>
     </row>
-    <row r="1298" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1298" t="s">
+    <row r="1298" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1298" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1298" s="9" t="s">
+      <c r="B1298" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1298" t="s">
+      <c r="C1298" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="D1298" t="s">
+      <c r="D1298" s="14" t="s">
         <v>1449</v>
       </c>
     </row>
-    <row r="1299" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1299" t="s">
+    <row r="1299" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1299" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1299" s="9" t="s">
+      <c r="B1299" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1299" t="s">
+      <c r="C1299" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="D1299" t="s">
+      <c r="D1299" s="14" t="s">
         <v>1450</v>
       </c>
     </row>
-    <row r="1300" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1300" t="s">
+    <row r="1300" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1300" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1300" s="9" t="s">
+      <c r="B1300" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1300" t="s">
+      <c r="C1300" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="D1300" t="s">
+      <c r="D1300" s="14" t="s">
         <v>1451</v>
       </c>
     </row>
-    <row r="1301" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1301" t="s">
+    <row r="1301" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1301" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1301" s="9" t="s">
+      <c r="B1301" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1301" t="s">
+      <c r="C1301" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="D1301" t="s">
+      <c r="D1301" s="14" t="s">
         <v>1452</v>
       </c>
     </row>
-    <row r="1302" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1302" t="s">
+    <row r="1302" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1302" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1302" s="9" t="s">
+      <c r="B1302" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1302" t="s">
+      <c r="C1302" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="D1302" t="s">
+      <c r="D1302" s="14" t="s">
         <v>1453</v>
       </c>
     </row>
-    <row r="1303" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1303" t="s">
+    <row r="1303" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1303" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1303" s="9" t="s">
+      <c r="B1303" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1303" t="s">
+      <c r="C1303" s="14" t="s">
         <v>563</v>
       </c>
-      <c r="D1303" t="s">
+      <c r="D1303" s="14" t="s">
         <v>1454</v>
       </c>
     </row>
-    <row r="1304" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1304" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1304" s="9" t="s">
+    <row r="1304" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1304" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1304" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1304" t="s">
+      <c r="C1304" s="14" t="s">
         <v>532</v>
       </c>
-      <c r="D1304" t="s">
+      <c r="D1304" s="14" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="1305" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1305" t="s">
+    <row r="1305" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1305" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1305" s="9" t="s">
+      <c r="B1305" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1305" t="s">
+      <c r="C1305" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="D1305" t="s">
+      <c r="D1305" s="14" t="s">
         <v>1456</v>
       </c>
     </row>
-    <row r="1306" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1306" t="s">
+    <row r="1306" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1306" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1306" s="9" t="s">
+      <c r="B1306" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1306" t="s">
+      <c r="C1306" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="D1306" t="s">
+      <c r="D1306" s="14" t="s">
         <v>1457</v>
       </c>
     </row>
-    <row r="1307" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1307" t="s">
+    <row r="1307" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1307" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1307" s="9" t="s">
+      <c r="B1307" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1307" t="s">
+      <c r="C1307" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="D1307" t="s">
+      <c r="D1307" s="14" t="s">
         <v>1458</v>
       </c>
     </row>
-    <row r="1308" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1308" t="s">
+    <row r="1308" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1308" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1308" s="9" t="s">
+      <c r="B1308" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1308" t="s">
+      <c r="C1308" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D1308" t="s">
+      <c r="D1308" s="14" t="s">
         <v>1459</v>
       </c>
     </row>
-    <row r="1309" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1309" t="s">
+    <row r="1309" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1309" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1309" s="9" t="s">
+      <c r="B1309" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1309" t="s">
+      <c r="C1309" s="14" t="s">
         <v>513</v>
       </c>
-      <c r="D1309" t="s">
+      <c r="D1309" s="14" t="s">
         <v>1460</v>
       </c>
     </row>
-    <row r="1310" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1310" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1310" s="9" t="s">
+    <row r="1310" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1310" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1310" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1310" t="s">
+      <c r="C1310" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="D1310" t="s">
+      <c r="D1310" s="14" t="s">
         <v>1461</v>
       </c>
     </row>
-    <row r="1311" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1311" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1311" s="9" t="s">
+    <row r="1311" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1311" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1311" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1311" t="s">
+      <c r="C1311" s="14" t="s">
         <v>532</v>
       </c>
-      <c r="D1311" t="s">
+      <c r="D1311" s="14" t="s">
         <v>1462</v>
       </c>
     </row>
-    <row r="1312" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1312" t="s">
+    <row r="1312" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1312" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1312" s="9" t="s">
+      <c r="B1312" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1312" t="s">
+      <c r="C1312" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="D1312" t="s">
+      <c r="D1312" s="14" t="s">
         <v>1463</v>
       </c>
     </row>
-    <row r="1313" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1313" t="s">
+    <row r="1313" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1313" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1313" s="9" t="s">
+      <c r="B1313" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1313" t="s">
+      <c r="C1313" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="D1313" t="s">
+      <c r="D1313" s="14" t="s">
         <v>1464</v>
       </c>
     </row>
-    <row r="1314" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1314" t="s">
+    <row r="1314" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1314" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1314" s="9" t="s">
+      <c r="B1314" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1314" t="s">
+      <c r="C1314" s="14" t="s">
         <v>674</v>
       </c>
-      <c r="D1314" t="s">
+      <c r="D1314" s="14" t="s">
         <v>1465</v>
       </c>
     </row>
-    <row r="1315" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1315" t="s">
+    <row r="1315" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1315" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1315" s="9" t="s">
+      <c r="B1315" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1315" t="s">
+      <c r="C1315" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="D1315" t="s">
+      <c r="D1315" s="14" t="s">
         <v>1466</v>
       </c>
     </row>
-    <row r="1316" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1316" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1316" s="9" t="s">
+    <row r="1316" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1316" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1316" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1316" t="s">
+      <c r="C1316" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="D1316" t="s">
+      <c r="D1316" s="14" t="s">
         <v>1467</v>
       </c>
     </row>
-    <row r="1317" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1317" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1317" s="9" t="s">
+    <row r="1317" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1317" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1317" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1317" t="s">
+      <c r="C1317" s="14" t="s">
         <v>532</v>
       </c>
-      <c r="D1317" t="s">
+      <c r="D1317" s="14" t="s">
         <v>1468</v>
       </c>
     </row>
-    <row r="1318" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1318" t="s">
+    <row r="1318" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1318" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1318" s="9" t="s">
+      <c r="B1318" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1318" t="s">
+      <c r="C1318" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="D1318" t="s">
+      <c r="D1318" s="14" t="s">
         <v>1469</v>
       </c>
     </row>
-    <row r="1319" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1319" t="s">
+    <row r="1319" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1319" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1319" s="9" t="s">
+      <c r="B1319" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1319" t="s">
+      <c r="C1319" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="D1319" t="s">
+      <c r="D1319" s="14" t="s">
         <v>1470</v>
       </c>
     </row>
-    <row r="1320" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1320" t="s">
+    <row r="1320" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1320" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1320" s="9" t="s">
+      <c r="B1320" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1320" t="s">
+      <c r="C1320" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="D1320" t="s">
+      <c r="D1320" s="14" t="s">
         <v>1471</v>
       </c>
     </row>
-    <row r="1321" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1321" t="s">
+    <row r="1321" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1321" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1321" s="9" t="s">
+      <c r="B1321" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1321" t="s">
+      <c r="C1321" s="14" t="s">
         <v>499</v>
       </c>
-      <c r="D1321" t="s">
+      <c r="D1321" s="14" t="s">
         <v>1472</v>
       </c>
     </row>
-    <row r="1322" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1322" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1322" s="9" t="s">
+    <row r="1322" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1322" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1322" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1322" t="s">
+      <c r="C1322" s="14" t="s">
         <v>566</v>
       </c>
-      <c r="D1322" t="s">
+      <c r="D1322" s="14" t="s">
         <v>1473</v>
       </c>
     </row>
-    <row r="1323" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1323" t="s">
+    <row r="1323" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1323" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1323" s="9" t="s">
+      <c r="B1323" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1323" t="s">
+      <c r="C1323" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="D1323" t="s">
+      <c r="D1323" s="14" t="s">
         <v>1474</v>
       </c>
     </row>
-    <row r="1324" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1324" t="s">
+    <row r="1324" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1324" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1324" s="9" t="s">
+      <c r="B1324" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1324" t="s">
+      <c r="C1324" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="D1324" t="s">
+      <c r="D1324" s="14" t="s">
         <v>1475</v>
       </c>
     </row>
-    <row r="1325" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1325" t="s">
+    <row r="1325" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1325" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1325" s="9" t="s">
+      <c r="B1325" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1325" t="s">
+      <c r="C1325" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="D1325" t="s">
+      <c r="D1325" s="14" t="s">
         <v>1476</v>
       </c>
     </row>
-    <row r="1326" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1326" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1326" s="9" t="s">
+    <row r="1326" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1326" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1326" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1326" t="s">
+      <c r="C1326" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="D1326" t="s">
+      <c r="D1326" s="14" t="s">
         <v>1477</v>
       </c>
     </row>
-    <row r="1327" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1327" t="s">
+    <row r="1327" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1327" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1327" s="9" t="s">
+      <c r="B1327" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1327" t="s">
+      <c r="C1327" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="D1327" t="s">
+      <c r="D1327" s="14" t="s">
         <v>1478</v>
       </c>
     </row>
-    <row r="1328" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1328" t="s">
+    <row r="1328" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1328" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1328" s="9" t="s">
+      <c r="B1328" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1328" t="s">
+      <c r="C1328" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="D1328" t="s">
+      <c r="D1328" s="14" t="s">
         <v>1479</v>
       </c>
     </row>
-    <row r="1329" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1329" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1329" s="9" t="s">
+    <row r="1329" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1329" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1329" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1329" t="s">
+      <c r="C1329" s="14" t="s">
         <v>560</v>
       </c>
-      <c r="D1329" t="s">
+      <c r="D1329" s="14" t="s">
         <v>1480</v>
       </c>
     </row>
-    <row r="1330" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1330" t="s">
+    <row r="1330" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1330" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1330" s="9" t="s">
+      <c r="B1330" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1330" t="s">
+      <c r="C1330" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="D1330" t="s">
+      <c r="D1330" s="14" t="s">
         <v>1481</v>
       </c>
     </row>
-    <row r="1331" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1331" t="s">
+    <row r="1331" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1331" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1331" s="9" t="s">
+      <c r="B1331" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1331" t="s">
+      <c r="C1331" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="D1331" t="s">
+      <c r="D1331" s="14" t="s">
         <v>1482</v>
       </c>
     </row>
-    <row r="1332" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1332" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1332" s="9" t="s">
+    <row r="1332" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1332" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1332" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1332" t="s">
+      <c r="C1332" s="14" t="s">
         <v>566</v>
       </c>
-      <c r="D1332" t="s">
+      <c r="D1332" s="14" t="s">
         <v>1483</v>
       </c>
     </row>
-    <row r="1333" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1333" t="s">
+    <row r="1333" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1333" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1333" s="9" t="s">
+      <c r="B1333" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1333" t="s">
+      <c r="C1333" s="14" t="s">
         <v>569</v>
       </c>
-      <c r="D1333" t="s">
+      <c r="D1333" s="14" t="s">
         <v>1484</v>
       </c>
     </row>
-    <row r="1334" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1334" t="s">
+    <row r="1334" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1334" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1334" s="9" t="s">
+      <c r="B1334" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1334" t="s">
+      <c r="C1334" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="D1334" t="s">
+      <c r="D1334" s="14" t="s">
         <v>1485</v>
       </c>
     </row>
-    <row r="1335" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1335" t="s">
+    <row r="1335" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1335" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1335" s="9" t="s">
+      <c r="B1335" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1335" t="s">
+      <c r="C1335" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="D1335" t="s">
+      <c r="D1335" s="14" t="s">
         <v>1486</v>
       </c>
     </row>
-    <row r="1336" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1336" t="s">
+    <row r="1336" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1336" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1336" s="9" t="s">
+      <c r="B1336" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1336" t="s">
+      <c r="C1336" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="D1336" t="s">
+      <c r="D1336" s="14" t="s">
         <v>1487</v>
       </c>
     </row>
-    <row r="1337" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1337" t="s">
+    <row r="1337" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1337" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1337" s="9" t="s">
+      <c r="B1337" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1337" t="s">
+      <c r="C1337" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="D1337" t="s">
+      <c r="D1337" s="14" t="s">
         <v>1488</v>
       </c>
     </row>
-    <row r="1338" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1338" t="s">
+    <row r="1338" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1338" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1338" s="9" t="s">
+      <c r="B1338" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1338" t="s">
+      <c r="C1338" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="D1338" t="s">
+      <c r="D1338" s="14" t="s">
         <v>1489</v>
       </c>
     </row>
-    <row r="1339" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1339" t="s">
+    <row r="1339" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1339" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1339" s="9" t="s">
+      <c r="B1339" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1339" t="s">
+      <c r="C1339" s="14" t="s">
         <v>470</v>
       </c>
-      <c r="D1339" t="s">
+      <c r="D1339" s="14" t="s">
         <v>1490</v>
       </c>
     </row>
-    <row r="1340" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1340" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1340" s="9" t="s">
+    <row r="1340" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1340" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1340" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1340" t="s">
+      <c r="C1340" s="14" t="s">
         <v>566</v>
       </c>
-      <c r="D1340" t="s">
+      <c r="D1340" s="14" t="s">
         <v>1491</v>
       </c>
     </row>
-    <row r="1341" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1341" t="s">
+    <row r="1341" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1341" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1341" s="9" t="s">
+      <c r="B1341" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1341" t="s">
+      <c r="C1341" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="D1341" t="s">
+      <c r="D1341" s="14" t="s">
         <v>1492</v>
       </c>
     </row>
-    <row r="1342" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1342" t="s">
+    <row r="1342" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1342" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1342" s="9" t="s">
+      <c r="B1342" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1342" t="s">
+      <c r="C1342" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="D1342" t="s">
+      <c r="D1342" s="14" t="s">
         <v>1493</v>
       </c>
     </row>
-    <row r="1343" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1343" t="s">
+    <row r="1343" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1343" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1343" s="9" t="s">
+      <c r="B1343" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1343" t="s">
+      <c r="C1343" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="D1343" t="s">
+      <c r="D1343" s="14" t="s">
         <v>1494</v>
       </c>
     </row>
-    <row r="1344" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1344" t="s">
+    <row r="1344" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1344" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1344" s="9" t="s">
+      <c r="B1344" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1344" t="s">
+      <c r="C1344" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="D1344" t="s">
+      <c r="D1344" s="14" t="s">
         <v>1495</v>
       </c>
     </row>
-    <row r="1345" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1345" t="s">
+    <row r="1345" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1345" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1345" s="9" t="s">
+      <c r="B1345" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1345" t="s">
+      <c r="C1345" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="D1345" t="s">
+      <c r="D1345" s="14" t="s">
         <v>1496</v>
       </c>
     </row>
-    <row r="1346" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1346" t="s">
+    <row r="1346" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1346" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1346" s="9" t="s">
+      <c r="B1346" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1346" t="s">
+      <c r="C1346" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D1346" t="s">
+      <c r="D1346" s="14" t="s">
         <v>1497</v>
       </c>
     </row>
-    <row r="1347" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1347" t="s">
+    <row r="1347" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1347" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1347" s="9" t="s">
+      <c r="B1347" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1347" t="s">
+      <c r="C1347" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="D1347" t="s">
+      <c r="D1347" s="14" t="s">
         <v>1498</v>
       </c>
     </row>
-    <row r="1348" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1348" t="s">
+    <row r="1348" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1348" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1348" s="9" t="s">
+      <c r="B1348" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1348" t="s">
+      <c r="C1348" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="D1348" t="s">
+      <c r="D1348" s="14" t="s">
         <v>1499</v>
       </c>
     </row>
-    <row r="1349" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1349" t="s">
+    <row r="1349" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1349" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1349" s="9" t="s">
+      <c r="B1349" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1349" t="s">
+      <c r="C1349" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="D1349" t="s">
+      <c r="D1349" s="14" t="s">
         <v>1500</v>
       </c>
     </row>
-    <row r="1350" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1350" t="s">
+    <row r="1350" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1350" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1350" s="9" t="s">
+      <c r="B1350" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1350" t="s">
+      <c r="C1350" s="14" t="s">
         <v>568</v>
       </c>
-      <c r="D1350" t="s">
+      <c r="D1350" s="14" t="s">
         <v>1501</v>
       </c>
     </row>
-    <row r="1351" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1351" t="s">
+    <row r="1351" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1351" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1351" s="9" t="s">
+      <c r="B1351" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1351" t="s">
+      <c r="C1351" s="14" t="s">
         <v>379</v>
       </c>
-      <c r="D1351" t="s">
+      <c r="D1351" s="14" t="s">
         <v>1502</v>
       </c>
     </row>
-    <row r="1352" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1352" t="s">
+    <row r="1352" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1352" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1352" s="9" t="s">
+      <c r="B1352" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1352" t="s">
+      <c r="C1352" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="D1352" t="s">
+      <c r="D1352" s="14" t="s">
         <v>1377</v>
       </c>
     </row>
-    <row r="1353" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1353" t="s">
+    <row r="1353" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1353" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1353" s="9" t="s">
+      <c r="B1353" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1353" t="s">
+      <c r="C1353" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="D1353" t="s">
+      <c r="D1353" s="14" t="s">
         <v>1378</v>
       </c>
     </row>
-    <row r="1354" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1354" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1354" s="9" t="s">
+    <row r="1354" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1354" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1354" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1354" t="s">
+      <c r="C1354" s="14" t="s">
         <v>532</v>
       </c>
-      <c r="D1354" t="s">
+      <c r="D1354" s="14" t="s">
         <v>1379</v>
       </c>
     </row>
-    <row r="1355" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1355" t="s">
+    <row r="1355" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1355" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1355" s="9" t="s">
+      <c r="B1355" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1355" t="s">
+      <c r="C1355" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="D1355" t="s">
+      <c r="D1355" s="14" t="s">
         <v>1380</v>
       </c>
     </row>
-    <row r="1356" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1356" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1356" s="9" t="s">
+    <row r="1356" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1356" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1356" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1356" t="s">
+      <c r="C1356" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="D1356" t="s">
+      <c r="D1356" s="14" t="s">
         <v>1381</v>
       </c>
     </row>
-    <row r="1357" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1357" t="s">
+    <row r="1357" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1357" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1357" s="9" t="s">
+      <c r="B1357" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1357" t="s">
+      <c r="C1357" s="14" t="s">
         <v>568</v>
       </c>
-      <c r="D1357" t="s">
+      <c r="D1357" s="14" t="s">
         <v>1382</v>
       </c>
     </row>
-    <row r="1358" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1358" t="s">
+    <row r="1358" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1358" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1358" s="9" t="s">
+      <c r="B1358" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1358" t="s">
+      <c r="C1358" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="D1358" t="s">
+      <c r="D1358" s="14" t="s">
         <v>1383</v>
       </c>
     </row>
-    <row r="1359" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1359" t="s">
+    <row r="1359" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1359" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1359" s="9" t="s">
+      <c r="B1359" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1359" t="s">
+      <c r="C1359" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="D1359" t="s">
+      <c r="D1359" s="14" t="s">
         <v>1384</v>
       </c>
     </row>
-    <row r="1360" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1360" t="s">
+    <row r="1360" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1360" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1360" s="9" t="s">
+      <c r="B1360" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1360" t="s">
+      <c r="C1360" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="D1360" t="s">
+      <c r="D1360" s="14" t="s">
         <v>1385</v>
       </c>
     </row>
-    <row r="1361" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1361" t="s">
+    <row r="1361" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1361" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1361" s="9" t="s">
+      <c r="B1361" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1361" t="s">
+      <c r="C1361" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="D1361" t="s">
+      <c r="D1361" s="14" t="s">
         <v>1386</v>
       </c>
     </row>
-    <row r="1362" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1362" t="s">
+    <row r="1362" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1362" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1362" s="9" t="s">
+      <c r="B1362" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1362" t="s">
+      <c r="C1362" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="D1362" t="s">
+      <c r="D1362" s="14" t="s">
         <v>1387</v>
       </c>
     </row>
-    <row r="1363" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1363" t="s">
+    <row r="1363" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1363" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1363" s="9" t="s">
+      <c r="B1363" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1363" t="s">
+      <c r="C1363" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="D1363" t="s">
+      <c r="D1363" s="14" t="s">
         <v>1388</v>
       </c>
     </row>
-    <row r="1364" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1364" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1364" s="9" t="s">
+    <row r="1364" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1364" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1364" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1364" t="s">
+      <c r="C1364" s="14" t="s">
         <v>535</v>
       </c>
-      <c r="D1364" t="s">
+      <c r="D1364" s="14" t="s">
         <v>1389</v>
       </c>
     </row>
-    <row r="1365" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1365" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1365" s="9" t="s">
+    <row r="1365" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1365" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1365" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1365" t="s">
+      <c r="C1365" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="D1365" t="s">
+      <c r="D1365" s="14" t="s">
         <v>1390</v>
       </c>
     </row>
-    <row r="1366" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1366" t="s">
+    <row r="1366" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1366" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1366" s="9" t="s">
+      <c r="B1366" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1366" t="s">
+      <c r="C1366" s="14" t="s">
         <v>466</v>
       </c>
-      <c r="D1366" t="s">
+      <c r="D1366" s="14" t="s">
         <v>1391</v>
       </c>
     </row>
-    <row r="1367" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1367" t="s">
+    <row r="1367" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1367" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1367" s="9" t="s">
+      <c r="B1367" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1367" t="s">
+      <c r="C1367" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="D1367" t="s">
+      <c r="D1367" s="14" t="s">
         <v>1392</v>
       </c>
     </row>
-    <row r="1368" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1368" t="s">
+    <row r="1368" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1368" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1368" s="9" t="s">
+      <c r="B1368" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1368" t="s">
+      <c r="C1368" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="D1368" t="s">
+      <c r="D1368" s="14" t="s">
         <v>1393</v>
       </c>
     </row>
-    <row r="1369" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1369" t="s">
+    <row r="1369" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1369" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1369" s="9" t="s">
+      <c r="B1369" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1369" t="s">
+      <c r="C1369" s="14" t="s">
         <v>568</v>
       </c>
-      <c r="D1369" t="s">
+      <c r="D1369" s="14" t="s">
         <v>1394</v>
       </c>
     </row>
-    <row r="1370" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1370" t="s">
+    <row r="1370" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1370" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1370" s="9" t="s">
+      <c r="B1370" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1370" t="s">
+      <c r="C1370" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="D1370" t="s">
+      <c r="D1370" s="14" t="s">
         <v>1395</v>
       </c>
     </row>
-    <row r="1371" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1371" t="s">
+    <row r="1371" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1371" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1371" s="9" t="s">
+      <c r="B1371" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1371" t="s">
+      <c r="C1371" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="D1371" t="s">
+      <c r="D1371" s="14" t="s">
         <v>1396</v>
       </c>
     </row>
-    <row r="1372" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1372" t="s">
+    <row r="1372" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1372" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1372" s="9" t="s">
+      <c r="B1372" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1372" t="s">
+      <c r="C1372" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="D1372" t="s">
+      <c r="D1372" s="14" t="s">
         <v>1397</v>
       </c>
     </row>
-    <row r="1373" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1373" t="s">
+    <row r="1373" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1373" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1373" s="9" t="s">
+      <c r="B1373" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1373" t="s">
+      <c r="C1373" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="D1373" t="s">
+      <c r="D1373" s="14" t="s">
         <v>1398</v>
       </c>
     </row>
-    <row r="1374" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1374" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1374" s="9" t="s">
+    <row r="1374" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1374" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1374" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C1374" t="s">
+      <c r="C1374" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="D1374" t="s">
+      <c r="D1374" s="14" t="s">
         <v>1503</v>
       </c>
     </row>
-    <row r="1375" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1375" t="s">
+    <row r="1375" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1375" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1375" s="9" t="s">
+      <c r="B1375" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1375" t="s">
+      <c r="C1375" s="14" t="s">
         <v>1505</v>
       </c>
-      <c r="D1375" t="s">
+      <c r="D1375" s="14" t="s">
         <v>1504</v>
       </c>
     </row>
-    <row r="1376" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1376" t="s">
+    <row r="1376" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1376" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1376" s="9" t="s">
+      <c r="B1376" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1376" t="s">
+      <c r="C1376" s="14" t="s">
         <v>1507</v>
       </c>
-      <c r="D1376" t="s">
+      <c r="D1376" s="14" t="s">
         <v>1506</v>
       </c>
     </row>
-    <row r="1377" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1377" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1377" s="9" t="s">
+    <row r="1377" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1377" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1377" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1377" t="s">
+      <c r="C1377" s="14" t="s">
         <v>1509</v>
       </c>
-      <c r="D1377" t="s">
+      <c r="D1377" s="14" t="s">
         <v>1508</v>
       </c>
     </row>
-    <row r="1378" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1378" t="s">
+    <row r="1378" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1378" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1378" s="9" t="s">
+      <c r="B1378" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1378" t="s">
+      <c r="C1378" s="14" t="s">
         <v>1511</v>
       </c>
-      <c r="D1378" t="s">
+      <c r="D1378" s="14" t="s">
         <v>1510</v>
       </c>
     </row>
-    <row r="1379" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1379" t="s">
+    <row r="1379" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1379" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1379" s="9" t="s">
+      <c r="B1379" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1379" t="s">
+      <c r="C1379" s="14" t="s">
         <v>1511</v>
       </c>
-      <c r="D1379" t="s">
+      <c r="D1379" s="14" t="s">
         <v>1512</v>
       </c>
     </row>
-    <row r="1380" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1380" t="s">
+    <row r="1380" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1380" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1380" s="9" t="s">
+      <c r="B1380" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1380" t="s">
+      <c r="C1380" s="14" t="s">
         <v>1514</v>
       </c>
-      <c r="D1380" t="s">
+      <c r="D1380" s="14" t="s">
         <v>1513</v>
       </c>
     </row>
-    <row r="1381" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1381" t="s">
+    <row r="1381" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1381" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1381" s="9" t="s">
+      <c r="B1381" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1381" t="s">
+      <c r="C1381" s="14" t="s">
         <v>1516</v>
       </c>
-      <c r="D1381" t="s">
+      <c r="D1381" s="14" t="s">
         <v>1515</v>
       </c>
     </row>
-    <row r="1382" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1382" t="s">
+    <row r="1382" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1382" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1382" s="9" t="s">
+      <c r="B1382" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1382" t="s">
+      <c r="C1382" s="14" t="s">
         <v>1518</v>
       </c>
-      <c r="D1382" t="s">
+      <c r="D1382" s="14" t="s">
         <v>1517</v>
       </c>
     </row>
-    <row r="1383" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1383" t="s">
+    <row r="1383" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1383" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1383" s="9" t="s">
+      <c r="B1383" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1383" t="s">
+      <c r="C1383" s="14" t="s">
         <v>1520</v>
       </c>
-      <c r="D1383" t="s">
+      <c r="D1383" s="14" t="s">
         <v>1519</v>
       </c>
     </row>
-    <row r="1384" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1384" t="s">
+    <row r="1384" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1384" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1384" s="9" t="s">
+      <c r="B1384" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1384" t="s">
+      <c r="C1384" s="14" t="s">
         <v>1511</v>
       </c>
-      <c r="D1384" t="s">
+      <c r="D1384" s="14" t="s">
         <v>1521</v>
       </c>
     </row>
-    <row r="1385" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1385" t="s">
+    <row r="1385" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1385" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1385" s="9" t="s">
+      <c r="B1385" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1385" t="s">
+      <c r="C1385" s="14" t="s">
         <v>1523</v>
       </c>
-      <c r="D1385" t="s">
+      <c r="D1385" s="14" t="s">
         <v>1522</v>
       </c>
     </row>
-    <row r="1386" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1386" t="s">
+    <row r="1386" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1386" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1386" s="9" t="s">
+      <c r="B1386" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1386" t="s">
+      <c r="C1386" s="14" t="s">
         <v>1525</v>
       </c>
-      <c r="D1386" t="s">
+      <c r="D1386" s="14" t="s">
         <v>1524</v>
       </c>
     </row>
-    <row r="1387" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1387" t="s">
+    <row r="1387" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1387" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1387" s="9" t="s">
+      <c r="B1387" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1387" t="s">
+      <c r="C1387" s="14" t="s">
         <v>1527</v>
       </c>
-      <c r="D1387" t="s">
+      <c r="D1387" s="14" t="s">
         <v>1526</v>
       </c>
     </row>
-    <row r="1388" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1388" t="s">
+    <row r="1388" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1388" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1388" s="9" t="s">
+      <c r="B1388" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1388" t="s">
+      <c r="C1388" s="14" t="s">
         <v>1529</v>
       </c>
-      <c r="D1388" t="s">
+      <c r="D1388" s="14" t="s">
         <v>1528</v>
       </c>
     </row>
-    <row r="1389" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1389" t="s">
+    <row r="1389" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1389" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1389" s="9" t="s">
+      <c r="B1389" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1389" t="s">
+      <c r="C1389" s="14" t="s">
         <v>1507</v>
       </c>
-      <c r="D1389" t="s">
+      <c r="D1389" s="14" t="s">
         <v>1530</v>
       </c>
     </row>
-    <row r="1390" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1390" t="s">
+    <row r="1390" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1390" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1390" s="9" t="s">
+      <c r="B1390" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1390" t="s">
+      <c r="C1390" s="14" t="s">
         <v>1529</v>
       </c>
-      <c r="D1390" t="s">
+      <c r="D1390" s="14" t="s">
         <v>1531</v>
       </c>
     </row>
-    <row r="1391" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1391" t="s">
+    <row r="1391" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1391" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1391" s="9" t="s">
+      <c r="B1391" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1391" t="s">
+      <c r="C1391" s="14" t="s">
         <v>1533</v>
       </c>
-      <c r="D1391" t="s">
+      <c r="D1391" s="14" t="s">
         <v>1532</v>
       </c>
     </row>
-    <row r="1392" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1392" t="s">
+    <row r="1392" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1392" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1392" s="9" t="s">
+      <c r="B1392" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1392" t="s">
+      <c r="C1392" s="14" t="s">
         <v>1527</v>
       </c>
-      <c r="D1392" t="s">
+      <c r="D1392" s="14" t="s">
         <v>1534</v>
       </c>
     </row>
-    <row r="1393" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1393" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1393" s="9" t="s">
+    <row r="1393" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1393" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1393" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1393" t="s">
+      <c r="C1393" s="14" t="s">
         <v>1536</v>
       </c>
-      <c r="D1393" t="s">
+      <c r="D1393" s="14" t="s">
         <v>1535</v>
       </c>
     </row>
-    <row r="1394" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1394" t="s">
+    <row r="1394" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1394" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1394" s="9" t="s">
+      <c r="B1394" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1394" t="s">
+      <c r="C1394" s="14" t="s">
         <v>1538</v>
       </c>
-      <c r="D1394" t="s">
+      <c r="D1394" s="14" t="s">
         <v>1537</v>
       </c>
     </row>
-    <row r="1395" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1395" t="s">
+    <row r="1395" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1395" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1395" s="9" t="s">
+      <c r="B1395" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1395" t="s">
+      <c r="C1395" s="14" t="s">
         <v>1540</v>
       </c>
-      <c r="D1395" t="s">
+      <c r="D1395" s="14" t="s">
         <v>1539</v>
       </c>
     </row>
-    <row r="1396" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1396" t="s">
+    <row r="1396" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1396" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1396" s="9" t="s">
+      <c r="B1396" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1396" t="s">
+      <c r="C1396" s="14" t="s">
         <v>1507</v>
       </c>
-      <c r="D1396" t="s">
+      <c r="D1396" s="14" t="s">
         <v>1541</v>
       </c>
     </row>
-    <row r="1397" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1397" t="s">
+    <row r="1397" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1397" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1397" s="9" t="s">
+      <c r="B1397" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1397" t="s">
+      <c r="C1397" s="14" t="s">
         <v>1543</v>
       </c>
-      <c r="D1397" t="s">
+      <c r="D1397" s="14" t="s">
         <v>1542</v>
       </c>
     </row>
-    <row r="1398" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1398" t="s">
+    <row r="1398" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1398" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1398" s="9" t="s">
+      <c r="B1398" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1398" t="s">
+      <c r="C1398" s="14" t="s">
         <v>1533</v>
       </c>
-      <c r="D1398" t="s">
+      <c r="D1398" s="14" t="s">
         <v>1544</v>
       </c>
     </row>
-    <row r="1399" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1399" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1399" s="9" t="s">
+    <row r="1399" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1399" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1399" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1399" t="s">
+      <c r="C1399" s="14" t="s">
         <v>1546</v>
       </c>
-      <c r="D1399" t="s">
+      <c r="D1399" s="14" t="s">
         <v>1545</v>
       </c>
     </row>
-    <row r="1400" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1400" t="s">
+    <row r="1400" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1400" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1400" s="9" t="s">
+      <c r="B1400" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1400" t="s">
+      <c r="C1400" s="14" t="s">
         <v>1548</v>
       </c>
-      <c r="D1400" t="s">
+      <c r="D1400" s="14" t="s">
         <v>1547</v>
       </c>
     </row>
-    <row r="1401" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1401" t="s">
+    <row r="1401" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1401" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1401" s="9" t="s">
+      <c r="B1401" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1401" t="s">
+      <c r="C1401" s="14" t="s">
         <v>1511</v>
       </c>
-      <c r="D1401" t="s">
+      <c r="D1401" s="14" t="s">
         <v>1549</v>
       </c>
     </row>
-    <row r="1402" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1402" t="s">
+    <row r="1402" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1402" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1402" s="9" t="s">
+      <c r="B1402" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1402" t="s">
+      <c r="C1402" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D1402" t="s">
+      <c r="D1402" s="14" t="s">
         <v>1550</v>
       </c>
     </row>
-    <row r="1403" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1403" t="s">
+    <row r="1403" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1403" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1403" s="9" t="s">
+      <c r="B1403" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1403" t="s">
+      <c r="C1403" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="D1403" t="s">
+      <c r="D1403" s="14" t="s">
         <v>1551</v>
       </c>
     </row>
-    <row r="1404" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1404" t="s">
+    <row r="1404" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1404" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1404" s="9" t="s">
+      <c r="B1404" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1404" t="s">
+      <c r="C1404" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="D1404" t="s">
+      <c r="D1404" s="14" t="s">
         <v>1552</v>
       </c>
     </row>
-    <row r="1405" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1405" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1405" s="9" t="s">
+    <row r="1405" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1405" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1405" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1405" t="s">
+      <c r="C1405" s="14" t="s">
         <v>535</v>
       </c>
-      <c r="D1405" t="s">
+      <c r="D1405" s="14" t="s">
         <v>1553</v>
       </c>
     </row>
-    <row r="1406" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1406" t="s">
+    <row r="1406" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1406" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1406" s="9" t="s">
+      <c r="B1406" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1406" t="s">
+      <c r="C1406" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="D1406" t="s">
+      <c r="D1406" s="14" t="s">
         <v>1554</v>
       </c>
     </row>
-    <row r="1407" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1407" t="s">
+    <row r="1407" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1407" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1407" s="9" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C1407" t="s">
+      <c r="B1407" s="16" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C1407" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="D1407" t="s">
+      <c r="D1407" s="14" t="s">
         <v>1555</v>
       </c>
     </row>
-    <row r="1408" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1408" t="s">
+    <row r="1408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1408" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B1408" s="9" t="s">
+      <c r="B1408" s="16" t="s">
         <v>1399</v>
       </c>
-      <c r="C1408" t="s">
+      <c r="C1408" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="D1408" s="18" t="s">
+      <c r="D1408" s="21" t="s">
         <v>1556</v>
       </c>
     </row>
-    <row r="1409" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1409" t="s">
+    <row r="1409" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1409" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1409" s="9" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C1409" t="s">
+      <c r="B1409" s="16" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C1409" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="D1409" t="s">
+      <c r="D1409" s="14" t="s">
         <v>1557</v>
       </c>
     </row>
     <row r="1410" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1410" t="s">
+      <c r="A1410" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1410" s="9" t="s">
+      <c r="B1410" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C1410" t="s">
+      <c r="C1410" s="14" t="s">
         <v>325</v>
       </c>
       <c r="D1410" s="3" t="s">
@@ -25357,17 +25381,45 @@
       </c>
     </row>
     <row r="1411" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1411" t="s">
+      <c r="A1411" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="B1411" s="9" t="s">
+      <c r="B1411" s="16" t="s">
         <v>1559</v>
       </c>
-      <c r="C1411" t="s">
+      <c r="C1411" s="14" t="s">
         <v>325</v>
       </c>
       <c r="D1411" s="3" t="s">
         <v>1560</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1412" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="B1412" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1412" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1412" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1413" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="B1413" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1413" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1413" t="s">
+        <v>1563</v>
       </c>
     </row>
   </sheetData>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -12,6 +12,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1411</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1411</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1411</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1566" count="1566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1568" count="1568">
   <si>
     <t>VINH</t>
   </si>
@@ -4721,6 +4722,12 @@
   </si>
   <si>
     <t>San Ha Pham The Hien 3102</t>
+  </si>
+  <si>
+    <t>Vinh</t>
+  </si>
+  <si>
+    <t>Gs25 Ta Quang Buu</t>
   </si>
 </sst>
 </file>
@@ -4842,7 +4849,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="bottom"/>
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
@@ -4941,11 +4948,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C6500"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5031,11 +5048,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF9C6500"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5076,16 +5093,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5412,7 +5419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E1414"/>
+  <dimension ref="A1:F1415"/>
   <sheetFormatPr defaultRowHeight="14.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="10.25" style="0"/>
@@ -25217,53 +25224,67 @@
         <v>1565</v>
       </c>
     </row>
+    <row r="1415" spans="8:8" ht="14.7">
+      <c r="A1415" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B1415" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>368</v>
+      </c>
+      <c r="D1415" t="s">
+        <v>1567</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D1411">
     <filterColumn colId="0" showButton="1"/>
   </autoFilter>
+  <conditionalFormatting sqref="A1:A1248">
+    <cfRule type="duplicateValues" priority="577" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="573" dxfId="1"/>
+    <cfRule type="duplicateValues" priority="572" dxfId="2"/>
+    <cfRule type="duplicateValues" priority="576" dxfId="3"/>
+    <cfRule type="duplicateValues" priority="574" dxfId="4"/>
+    <cfRule type="duplicateValues" priority="575" dxfId="5"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1211">
-    <cfRule type="duplicateValues" priority="584" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="585" dxfId="1"/>
-    <cfRule type="duplicateValues" priority="586" dxfId="2"/>
+    <cfRule type="duplicateValues" priority="584" dxfId="6"/>
+    <cfRule type="duplicateValues" priority="585" dxfId="7"/>
+    <cfRule type="duplicateValues" priority="586" dxfId="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A634:A644">
-    <cfRule type="duplicateValues" priority="18" dxfId="3"/>
+    <cfRule type="duplicateValues" priority="18" dxfId="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1247">
+    <cfRule type="duplicateValues" priority="4" dxfId="10"/>
+    <cfRule type="duplicateValues" priority="3" dxfId="11"/>
+    <cfRule type="duplicateValues" priority="5" dxfId="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1226 D1:D282 D284:D1204 D1210:D1224 C1205:C1209 D1246:D1407 D1409:D1048576">
-    <cfRule type="duplicateValues" priority="12" dxfId="4"/>
+    <cfRule type="duplicateValues" priority="12" dxfId="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1210:D1244 D1:D1204 C1205:C1209 D1246:D1407 D1409:D1048576">
+    <cfRule type="duplicateValues" priority="11" dxfId="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1246">
-    <cfRule type="duplicateValues" priority="6" dxfId="5"/>
-    <cfRule type="duplicateValues" priority="7" dxfId="6"/>
-    <cfRule type="duplicateValues" priority="8" dxfId="7"/>
+    <cfRule type="duplicateValues" priority="6" dxfId="15"/>
+    <cfRule type="duplicateValues" priority="8" dxfId="16"/>
+    <cfRule type="duplicateValues" priority="7" dxfId="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1248">
-    <cfRule type="duplicateValues" priority="575" dxfId="8"/>
-    <cfRule type="duplicateValues" priority="573" dxfId="9"/>
-    <cfRule type="duplicateValues" priority="576" dxfId="10"/>
-    <cfRule type="duplicateValues" priority="577" dxfId="11"/>
-    <cfRule type="duplicateValues" priority="574" dxfId="12"/>
-    <cfRule type="duplicateValues" priority="572" dxfId="13"/>
+  <conditionalFormatting sqref="A656:A658">
+    <cfRule type="duplicateValues" priority="17" dxfId="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1205:C1209 D1:D1204 D1210:D1407 D1409:D1048576">
+    <cfRule type="duplicateValues" priority="10" dxfId="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A576:A1248 A1:A572">
-    <cfRule type="duplicateValues" priority="569" dxfId="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1247">
-    <cfRule type="duplicateValues" priority="5" dxfId="15"/>
-    <cfRule type="duplicateValues" priority="4" dxfId="16"/>
-    <cfRule type="duplicateValues" priority="3" dxfId="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1210:D1244 D1:D1204 C1205:C1209 D1246:D1407 D1409:D1048576">
-    <cfRule type="duplicateValues" priority="11" dxfId="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A656:A658">
-    <cfRule type="duplicateValues" priority="17" dxfId="19"/>
+    <cfRule type="duplicateValues" priority="569" dxfId="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1408">
-    <cfRule type="duplicateValues" priority="2" dxfId="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1205:C1209 D1:D1204 D1210:D1407 D1409:D1048576">
-    <cfRule type="duplicateValues" priority="10" dxfId="21"/>
+    <cfRule type="duplicateValues" priority="2" dxfId="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="duplicateValues" priority="1" dxfId="22"/>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1415</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1411</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1411</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1411</definedName>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1568" count="1568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1573" count="1573">
   <si>
     <t>VINH</t>
   </si>
@@ -4728,6 +4729,21 @@
   </si>
   <si>
     <t>Gs25 Ta Quang Buu</t>
+  </si>
+  <si>
+    <t>Hien</t>
+  </si>
+  <si>
+    <t>GS25 14 Bui Vien</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>BHX NGUYEN THI NHUAN</t>
+  </si>
+  <si>
+    <t>Phuong Pham Ngu Lao</t>
   </si>
 </sst>
 </file>
@@ -4948,6 +4964,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -5048,26 +5104,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -5093,26 +5129,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5419,7 +5435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F1415"/>
+  <dimension ref="A1:E1417"/>
   <sheetFormatPr defaultRowHeight="14.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="10.25" style="0"/>
@@ -25226,7 +25242,7 @@
     </row>
     <row r="1415" spans="8:8" ht="14.7">
       <c r="A1415" t="s">
-        <v>1566</v>
+        <v>0</v>
       </c>
       <c r="B1415" s="1" t="s">
         <v>17</v>
@@ -25238,56 +25254,84 @@
         <v>1567</v>
       </c>
     </row>
+    <row r="1416" spans="8:8" ht="14.7">
+      <c r="A1416" t="s">
+        <v>322</v>
+      </c>
+      <c r="B1416" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D1416" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="1417" spans="8:8" ht="14.7">
+      <c r="A1417" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1417" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C1417" t="s">
+        <v>562</v>
+      </c>
+      <c r="D1417" t="s">
+        <v>1571</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D1411">
+  <autoFilter ref="A1:D1415">
     <filterColumn colId="0" showButton="1"/>
   </autoFilter>
+  <conditionalFormatting sqref="B1:B1211">
+    <cfRule type="duplicateValues" priority="584" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="585" dxfId="1"/>
+    <cfRule type="duplicateValues" priority="586" dxfId="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1248">
-    <cfRule type="duplicateValues" priority="577" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="573" dxfId="1"/>
-    <cfRule type="duplicateValues" priority="572" dxfId="2"/>
-    <cfRule type="duplicateValues" priority="576" dxfId="3"/>
-    <cfRule type="duplicateValues" priority="574" dxfId="4"/>
-    <cfRule type="duplicateValues" priority="575" dxfId="5"/>
+    <cfRule type="duplicateValues" priority="574" dxfId="3"/>
+    <cfRule type="duplicateValues" priority="577" dxfId="4"/>
+    <cfRule type="duplicateValues" priority="576" dxfId="5"/>
+    <cfRule type="duplicateValues" priority="575" dxfId="6"/>
+    <cfRule type="duplicateValues" priority="573" dxfId="7"/>
+    <cfRule type="duplicateValues" priority="572" dxfId="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1211">
-    <cfRule type="duplicateValues" priority="584" dxfId="6"/>
-    <cfRule type="duplicateValues" priority="585" dxfId="7"/>
-    <cfRule type="duplicateValues" priority="586" dxfId="8"/>
+  <conditionalFormatting sqref="C1205:C1209 D1:D1204 D1210:D1407 D1409:D1048576">
+    <cfRule type="duplicateValues" priority="10" dxfId="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A576:A1248 A1:A572">
+    <cfRule type="duplicateValues" priority="569" dxfId="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1226 D1:D282 D284:D1204 D1210:D1224 C1205:C1209 D1246:D1407 D1409:D1048576">
+    <cfRule type="duplicateValues" priority="12" dxfId="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1247">
+    <cfRule type="duplicateValues" priority="5" dxfId="12"/>
+    <cfRule type="duplicateValues" priority="3" dxfId="13"/>
+    <cfRule type="duplicateValues" priority="4" dxfId="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A634:A644">
-    <cfRule type="duplicateValues" priority="18" dxfId="9"/>
+    <cfRule type="duplicateValues" priority="18" dxfId="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1247">
-    <cfRule type="duplicateValues" priority="4" dxfId="10"/>
-    <cfRule type="duplicateValues" priority="3" dxfId="11"/>
-    <cfRule type="duplicateValues" priority="5" dxfId="12"/>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="duplicateValues" priority="1" dxfId="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1226 D1:D282 D284:D1204 D1210:D1224 C1205:C1209 D1246:D1407 D1409:D1048576">
-    <cfRule type="duplicateValues" priority="12" dxfId="13"/>
+  <conditionalFormatting sqref="B1246">
+    <cfRule type="duplicateValues" priority="7" dxfId="17"/>
+    <cfRule type="duplicateValues" priority="8" dxfId="18"/>
+    <cfRule type="duplicateValues" priority="6" dxfId="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1210:D1244 D1:D1204 C1205:C1209 D1246:D1407 D1409:D1048576">
-    <cfRule type="duplicateValues" priority="11" dxfId="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1246">
-    <cfRule type="duplicateValues" priority="6" dxfId="15"/>
-    <cfRule type="duplicateValues" priority="8" dxfId="16"/>
-    <cfRule type="duplicateValues" priority="7" dxfId="17"/>
+    <cfRule type="duplicateValues" priority="11" dxfId="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A656:A658">
-    <cfRule type="duplicateValues" priority="17" dxfId="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1205:C1209 D1:D1204 D1210:D1407 D1409:D1048576">
-    <cfRule type="duplicateValues" priority="10" dxfId="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A576:A1248 A1:A572">
-    <cfRule type="duplicateValues" priority="569" dxfId="20"/>
+    <cfRule type="duplicateValues" priority="17" dxfId="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1408">
-    <cfRule type="duplicateValues" priority="2" dxfId="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" priority="1" dxfId="22"/>
+    <cfRule type="duplicateValues" priority="2" dxfId="22"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data nhan vien.xlsx
+++ b/data nhan vien.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1415</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1415</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1411</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1411</definedName>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1573" count="1573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1574" count="1574">
   <si>
     <t>VINH</t>
   </si>
@@ -4744,6 +4745,9 @@
   </si>
   <si>
     <t>Phuong Pham Ngu Lao</t>
+  </si>
+  <si>
+    <t>BHX 38D Cay Keo</t>
   </si>
 </sst>
 </file>
@@ -4994,6 +4998,56 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -5079,56 +5133,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5435,7 +5439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E1417"/>
+  <dimension ref="A1:F1418"/>
   <sheetFormatPr defaultRowHeight="14.25" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="10.25" style="0"/>
@@ -25282,56 +25286,70 @@
         <v>1571</v>
       </c>
     </row>
+    <row r="1418" spans="8:8" ht="14.7">
+      <c r="A1418" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1418" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C1418" t="s">
+        <v>363</v>
+      </c>
+      <c r="D1418" t="s">
+        <v>1573</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D1415">
     <filterColumn colId="0" showButton="1"/>
   </autoFilter>
+  <conditionalFormatting sqref="D1226 D1:D282 D284:D1204 D1210:D1224 C1205:C1209 D1246:D1407 D1409:D1048576">
+    <cfRule type="duplicateValues" priority="12" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1247">
+    <cfRule type="duplicateValues" priority="3" dxfId="1"/>
+    <cfRule type="duplicateValues" priority="5" dxfId="2"/>
+    <cfRule type="duplicateValues" priority="4" dxfId="3"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1211">
-    <cfRule type="duplicateValues" priority="584" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="585" dxfId="1"/>
-    <cfRule type="duplicateValues" priority="586" dxfId="2"/>
+    <cfRule type="duplicateValues" priority="584" dxfId="4"/>
+    <cfRule type="duplicateValues" priority="586" dxfId="5"/>
+    <cfRule type="duplicateValues" priority="585" dxfId="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1248">
-    <cfRule type="duplicateValues" priority="574" dxfId="3"/>
-    <cfRule type="duplicateValues" priority="577" dxfId="4"/>
-    <cfRule type="duplicateValues" priority="576" dxfId="5"/>
-    <cfRule type="duplicateValues" priority="575" dxfId="6"/>
-    <cfRule type="duplicateValues" priority="573" dxfId="7"/>
-    <cfRule type="duplicateValues" priority="572" dxfId="8"/>
+    <cfRule type="duplicateValues" priority="574" dxfId="7"/>
+    <cfRule type="duplicateValues" priority="577" dxfId="8"/>
+    <cfRule type="duplicateValues" priority="576" dxfId="9"/>
+    <cfRule type="duplicateValues" priority="575" dxfId="10"/>
+    <cfRule type="duplicateValues" priority="573" dxfId="11"/>
+    <cfRule type="duplicateValues" priority="572" dxfId="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1210:D1244 D1:D1204 C1205:C1209 D1246:D1407 D1409:D1048576">
+    <cfRule type="duplicateValues" priority="11" dxfId="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="duplicateValues" priority="1" dxfId="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1246">
+    <cfRule type="duplicateValues" priority="7" dxfId="15"/>
+    <cfRule type="duplicateValues" priority="6" dxfId="16"/>
+    <cfRule type="duplicateValues" priority="8" dxfId="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1408">
+    <cfRule type="duplicateValues" priority="2" dxfId="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A634:A644">
+    <cfRule type="duplicateValues" priority="18" dxfId="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A576:A1248 A1:A572">
+    <cfRule type="duplicateValues" priority="569" dxfId="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1205:C1209 D1:D1204 D1210:D1407 D1409:D1048576">
-    <cfRule type="duplicateValues" priority="10" dxfId="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A576:A1248 A1:A572">
-    <cfRule type="duplicateValues" priority="569" dxfId="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1226 D1:D282 D284:D1204 D1210:D1224 C1205:C1209 D1246:D1407 D1409:D1048576">
-    <cfRule type="duplicateValues" priority="12" dxfId="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1247">
-    <cfRule type="duplicateValues" priority="5" dxfId="12"/>
-    <cfRule type="duplicateValues" priority="3" dxfId="13"/>
-    <cfRule type="duplicateValues" priority="4" dxfId="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A634:A644">
-    <cfRule type="duplicateValues" priority="18" dxfId="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" priority="1" dxfId="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1246">
-    <cfRule type="duplicateValues" priority="7" dxfId="17"/>
-    <cfRule type="duplicateValues" priority="8" dxfId="18"/>
-    <cfRule type="duplicateValues" priority="6" dxfId="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1210:D1244 D1:D1204 C1205:C1209 D1246:D1407 D1409:D1048576">
-    <cfRule type="duplicateValues" priority="11" dxfId="20"/>
+    <cfRule type="duplicateValues" priority="10" dxfId="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A656:A658">
-    <cfRule type="duplicateValues" priority="17" dxfId="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1408">
-    <cfRule type="duplicateValues" priority="2" dxfId="22"/>
+    <cfRule type="duplicateValues" priority="17" dxfId="22"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
